--- a/GT_gpt5_2_1.xlsx
+++ b/GT_gpt5_2_1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkats\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC1C458A-69F6-4F0E-9430-BEE4305DE641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{91D4C75B-B2CD-4F57-8278-FDCAB022D852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{1A97D13F-CB94-4389-AE4C-B08FCB49E1FC}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{A3F4C6B1-7A32-46D0-81EC-1870D7AD2687}"/>
   </bookViews>
   <sheets>
     <sheet name="GT_gpt5_2_1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4441" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5925" uniqueCount="765">
   <si>
     <t>ID</t>
   </si>
@@ -1751,6 +1751,570 @@
   </si>
   <si>
     <t>pat0540</t>
+  </si>
+  <si>
+    <t>pat0541</t>
+  </si>
+  <si>
+    <t>pat0542</t>
+  </si>
+  <si>
+    <t>pat0543</t>
+  </si>
+  <si>
+    <t>pat0544</t>
+  </si>
+  <si>
+    <t>pat0545</t>
+  </si>
+  <si>
+    <t>pat0546</t>
+  </si>
+  <si>
+    <t>pat0547</t>
+  </si>
+  <si>
+    <t>pat0548</t>
+  </si>
+  <si>
+    <t>pat0549</t>
+  </si>
+  <si>
+    <t>pat0550</t>
+  </si>
+  <si>
+    <t>pat0551</t>
+  </si>
+  <si>
+    <t>pat0552</t>
+  </si>
+  <si>
+    <t>pat0553</t>
+  </si>
+  <si>
+    <t>pat0554</t>
+  </si>
+  <si>
+    <t>pat0555</t>
+  </si>
+  <si>
+    <t>pat0556</t>
+  </si>
+  <si>
+    <t>pat0557</t>
+  </si>
+  <si>
+    <t>pat0558</t>
+  </si>
+  <si>
+    <t>pat0559</t>
+  </si>
+  <si>
+    <t>pat0560</t>
+  </si>
+  <si>
+    <t>pat0561</t>
+  </si>
+  <si>
+    <t>pat0562</t>
+  </si>
+  <si>
+    <t>pat0563</t>
+  </si>
+  <si>
+    <t>pat0564</t>
+  </si>
+  <si>
+    <t>pat0565</t>
+  </si>
+  <si>
+    <t>pat0566</t>
+  </si>
+  <si>
+    <t>pat0567</t>
+  </si>
+  <si>
+    <t>pat0568</t>
+  </si>
+  <si>
+    <t>pat0569</t>
+  </si>
+  <si>
+    <t>pat0570</t>
+  </si>
+  <si>
+    <t>pat0571</t>
+  </si>
+  <si>
+    <t>pat0572</t>
+  </si>
+  <si>
+    <t>pat0573</t>
+  </si>
+  <si>
+    <t>pat0574</t>
+  </si>
+  <si>
+    <t>pat0575</t>
+  </si>
+  <si>
+    <t>pat0576</t>
+  </si>
+  <si>
+    <t>pat0577</t>
+  </si>
+  <si>
+    <t>pat0578</t>
+  </si>
+  <si>
+    <t>pat0579</t>
+  </si>
+  <si>
+    <t>pat0580</t>
+  </si>
+  <si>
+    <t>pat0581</t>
+  </si>
+  <si>
+    <t>pat0582</t>
+  </si>
+  <si>
+    <t>pat0583</t>
+  </si>
+  <si>
+    <t>pat0584</t>
+  </si>
+  <si>
+    <t>pat0585</t>
+  </si>
+  <si>
+    <t>pat0586</t>
+  </si>
+  <si>
+    <t>pat0587</t>
+  </si>
+  <si>
+    <t>pat0588</t>
+  </si>
+  <si>
+    <t>pat0589</t>
+  </si>
+  <si>
+    <t>pat0590</t>
+  </si>
+  <si>
+    <t>pat0591</t>
+  </si>
+  <si>
+    <t>pat0592</t>
+  </si>
+  <si>
+    <t>pat0593</t>
+  </si>
+  <si>
+    <t>pat0594</t>
+  </si>
+  <si>
+    <t>pat0595</t>
+  </si>
+  <si>
+    <t>pat0596</t>
+  </si>
+  <si>
+    <t>pat0597</t>
+  </si>
+  <si>
+    <t>pat0598</t>
+  </si>
+  <si>
+    <t>pat0599</t>
+  </si>
+  <si>
+    <t>pat0600</t>
+  </si>
+  <si>
+    <t>pat0601</t>
+  </si>
+  <si>
+    <t>pat0602</t>
+  </si>
+  <si>
+    <t>pat0603</t>
+  </si>
+  <si>
+    <t>pat0604</t>
+  </si>
+  <si>
+    <t>pat0605</t>
+  </si>
+  <si>
+    <t>pat0606</t>
+  </si>
+  <si>
+    <t>pat0607</t>
+  </si>
+  <si>
+    <t>pat0608</t>
+  </si>
+  <si>
+    <t>pat0609</t>
+  </si>
+  <si>
+    <t>pat0610</t>
+  </si>
+  <si>
+    <t>pat0611</t>
+  </si>
+  <si>
+    <t>pat0612</t>
+  </si>
+  <si>
+    <t>pat0613</t>
+  </si>
+  <si>
+    <t>pat0614</t>
+  </si>
+  <si>
+    <t>pat0615</t>
+  </si>
+  <si>
+    <t>pat0616</t>
+  </si>
+  <si>
+    <t>pat0617</t>
+  </si>
+  <si>
+    <t>pat0618</t>
+  </si>
+  <si>
+    <t>pat0619</t>
+  </si>
+  <si>
+    <t>pat0620</t>
+  </si>
+  <si>
+    <t>pat0621</t>
+  </si>
+  <si>
+    <t>pat0622</t>
+  </si>
+  <si>
+    <t>pat0623</t>
+  </si>
+  <si>
+    <t>pat0624</t>
+  </si>
+  <si>
+    <t>pat0625</t>
+  </si>
+  <si>
+    <t>pat0626</t>
+  </si>
+  <si>
+    <t>pat0627</t>
+  </si>
+  <si>
+    <t>pat0628</t>
+  </si>
+  <si>
+    <t>pat0629</t>
+  </si>
+  <si>
+    <t>pat0630</t>
+  </si>
+  <si>
+    <t>pat0631</t>
+  </si>
+  <si>
+    <t>pat0632</t>
+  </si>
+  <si>
+    <t>pat0633</t>
+  </si>
+  <si>
+    <t>pat0634</t>
+  </si>
+  <si>
+    <t>pat0635</t>
+  </si>
+  <si>
+    <t>pat0636</t>
+  </si>
+  <si>
+    <t>pat0637</t>
+  </si>
+  <si>
+    <t>pat0638</t>
+  </si>
+  <si>
+    <t>pat0639</t>
+  </si>
+  <si>
+    <t>pat0640</t>
+  </si>
+  <si>
+    <t>pat0641</t>
+  </si>
+  <si>
+    <t>pat0642</t>
+  </si>
+  <si>
+    <t>pat0643</t>
+  </si>
+  <si>
+    <t>pat0644</t>
+  </si>
+  <si>
+    <t>pat0645</t>
+  </si>
+  <si>
+    <t>pat0646</t>
+  </si>
+  <si>
+    <t>pat0647</t>
+  </si>
+  <si>
+    <t>pat0648</t>
+  </si>
+  <si>
+    <t>pat0649</t>
+  </si>
+  <si>
+    <t>pat0650</t>
+  </si>
+  <si>
+    <t>pat0651</t>
+  </si>
+  <si>
+    <t>pat0652</t>
+  </si>
+  <si>
+    <t>pat0653</t>
+  </si>
+  <si>
+    <t>pat0654</t>
+  </si>
+  <si>
+    <t>pat0655</t>
+  </si>
+  <si>
+    <t>pat0656</t>
+  </si>
+  <si>
+    <t>pat0657</t>
+  </si>
+  <si>
+    <t>pat0658</t>
+  </si>
+  <si>
+    <t>pat0659</t>
+  </si>
+  <si>
+    <t>pat0660</t>
+  </si>
+  <si>
+    <t>pat0661</t>
+  </si>
+  <si>
+    <t>pat0662</t>
+  </si>
+  <si>
+    <t>pat0663</t>
+  </si>
+  <si>
+    <t>pat0664</t>
+  </si>
+  <si>
+    <t>pat0665</t>
+  </si>
+  <si>
+    <t>pat0666</t>
+  </si>
+  <si>
+    <t>pat0667</t>
+  </si>
+  <si>
+    <t>pat0668</t>
+  </si>
+  <si>
+    <t>pat0669</t>
+  </si>
+  <si>
+    <t>pat0670</t>
+  </si>
+  <si>
+    <t>pat0671</t>
+  </si>
+  <si>
+    <t>pat0672</t>
+  </si>
+  <si>
+    <t>pat0673</t>
+  </si>
+  <si>
+    <t>pat0674</t>
+  </si>
+  <si>
+    <t>pat0675</t>
+  </si>
+  <si>
+    <t>pat0676</t>
+  </si>
+  <si>
+    <t>pat0677</t>
+  </si>
+  <si>
+    <t>pat0678</t>
+  </si>
+  <si>
+    <t>pat0679</t>
+  </si>
+  <si>
+    <t>pat0680</t>
+  </si>
+  <si>
+    <t>pat0681</t>
+  </si>
+  <si>
+    <t>pat0682</t>
+  </si>
+  <si>
+    <t>pat0683</t>
+  </si>
+  <si>
+    <t>pat0684</t>
+  </si>
+  <si>
+    <t>pat0685</t>
+  </si>
+  <si>
+    <t>pat0686</t>
+  </si>
+  <si>
+    <t>pat0687</t>
+  </si>
+  <si>
+    <t>pat0688</t>
+  </si>
+  <si>
+    <t>pat0689</t>
+  </si>
+  <si>
+    <t>pat0690</t>
+  </si>
+  <si>
+    <t>pat0691</t>
+  </si>
+  <si>
+    <t>pat0692</t>
+  </si>
+  <si>
+    <t>pat0693</t>
+  </si>
+  <si>
+    <t>pat0694</t>
+  </si>
+  <si>
+    <t>pat0695</t>
+  </si>
+  <si>
+    <t>pat0696</t>
+  </si>
+  <si>
+    <t>pat0697</t>
+  </si>
+  <si>
+    <t>pat0698</t>
+  </si>
+  <si>
+    <t>pat0699</t>
+  </si>
+  <si>
+    <t>pat0700</t>
+  </si>
+  <si>
+    <t>pat0701</t>
+  </si>
+  <si>
+    <t>pat0702</t>
+  </si>
+  <si>
+    <t>pat0703</t>
+  </si>
+  <si>
+    <t>pat0704</t>
+  </si>
+  <si>
+    <t>pat0705</t>
+  </si>
+  <si>
+    <t>pat0706</t>
+  </si>
+  <si>
+    <t>pat0707</t>
+  </si>
+  <si>
+    <t>pat0708</t>
+  </si>
+  <si>
+    <t>pat0709</t>
+  </si>
+  <si>
+    <t>pat0710</t>
+  </si>
+  <si>
+    <t>pat0711</t>
+  </si>
+  <si>
+    <t>pat0712</t>
+  </si>
+  <si>
+    <t>pat0713</t>
+  </si>
+  <si>
+    <t>pat0714</t>
+  </si>
+  <si>
+    <t>pat0715</t>
+  </si>
+  <si>
+    <t>pat0716</t>
+  </si>
+  <si>
+    <t>pat0717</t>
+  </si>
+  <si>
+    <t>pat0718</t>
+  </si>
+  <si>
+    <t>pat0719</t>
+  </si>
+  <si>
+    <t>pat0720</t>
+  </si>
+  <si>
+    <t>pat0721</t>
+  </si>
+  <si>
+    <t>pat0722</t>
+  </si>
+  <si>
+    <t>pat0723</t>
+  </si>
+  <si>
+    <t>pat0724</t>
+  </si>
+  <si>
+    <t>pat0725</t>
+  </si>
+  <si>
+    <t>pat0726</t>
+  </si>
+  <si>
+    <t>pat0727</t>
+  </si>
+  <si>
+    <t>pat0728</t>
   </si>
 </sst>
 </file>
@@ -2610,8 +3174,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CEA479D-E8B4-4688-881A-F9910A250BEF}">
-  <dimension ref="A1:P541"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF64FC0F-79AA-4BD0-8E97-9F270AE34A33}">
+  <dimension ref="A1:P729"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.4">
@@ -20187,6 +20751,5917 @@
         <v>38</v>
       </c>
     </row>
+    <row r="542" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A542" t="s">
+        <v>577</v>
+      </c>
+      <c r="B542">
+        <v>6</v>
+      </c>
+      <c r="C542" t="s">
+        <v>17</v>
+      </c>
+      <c r="D542" t="s">
+        <v>34</v>
+      </c>
+      <c r="E542" t="s">
+        <v>25</v>
+      </c>
+      <c r="F542" t="s">
+        <v>20</v>
+      </c>
+      <c r="H542" t="s">
+        <v>42</v>
+      </c>
+      <c r="I542">
+        <v>3</v>
+      </c>
+      <c r="J542" t="s">
+        <v>17</v>
+      </c>
+      <c r="N542" t="s">
+        <v>17</v>
+      </c>
+      <c r="O542" t="s">
+        <v>48</v>
+      </c>
+      <c r="P542" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="543" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A543" t="s">
+        <v>578</v>
+      </c>
+      <c r="B543">
+        <v>2</v>
+      </c>
+      <c r="C543" t="s">
+        <v>17</v>
+      </c>
+      <c r="D543" t="s">
+        <v>55</v>
+      </c>
+      <c r="F543" t="s">
+        <v>17</v>
+      </c>
+      <c r="J543" t="s">
+        <v>17</v>
+      </c>
+      <c r="N543" t="s">
+        <v>17</v>
+      </c>
+      <c r="P543" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="544" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A544" t="s">
+        <v>579</v>
+      </c>
+      <c r="B544">
+        <v>2</v>
+      </c>
+      <c r="C544" t="s">
+        <v>20</v>
+      </c>
+      <c r="D544" t="s">
+        <v>27</v>
+      </c>
+      <c r="E544" t="s">
+        <v>25</v>
+      </c>
+      <c r="F544" t="s">
+        <v>20</v>
+      </c>
+      <c r="I544">
+        <v>7</v>
+      </c>
+      <c r="J544" t="s">
+        <v>17</v>
+      </c>
+      <c r="N544" t="s">
+        <v>17</v>
+      </c>
+      <c r="O544">
+        <v>1</v>
+      </c>
+      <c r="P544" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="545" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A545" t="s">
+        <v>580</v>
+      </c>
+      <c r="B545">
+        <v>2</v>
+      </c>
+      <c r="C545" t="s">
+        <v>20</v>
+      </c>
+      <c r="D545" t="s">
+        <v>34</v>
+      </c>
+      <c r="E545" t="s">
+        <v>25</v>
+      </c>
+      <c r="F545" t="s">
+        <v>20</v>
+      </c>
+      <c r="I545">
+        <v>13</v>
+      </c>
+      <c r="J545" t="s">
+        <v>17</v>
+      </c>
+      <c r="N545" t="s">
+        <v>17</v>
+      </c>
+      <c r="O545">
+        <v>1</v>
+      </c>
+      <c r="P545" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="546" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A546" t="s">
+        <v>581</v>
+      </c>
+      <c r="B546">
+        <v>1</v>
+      </c>
+      <c r="C546" t="s">
+        <v>17</v>
+      </c>
+      <c r="D546" t="s">
+        <v>18</v>
+      </c>
+      <c r="E546" t="s">
+        <v>25</v>
+      </c>
+      <c r="F546" t="s">
+        <v>17</v>
+      </c>
+      <c r="J546" t="s">
+        <v>17</v>
+      </c>
+      <c r="N546" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="547" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A547" t="s">
+        <v>582</v>
+      </c>
+      <c r="B547">
+        <v>2</v>
+      </c>
+      <c r="C547" t="s">
+        <v>20</v>
+      </c>
+      <c r="D547" t="s">
+        <v>34</v>
+      </c>
+      <c r="E547" t="s">
+        <v>25</v>
+      </c>
+      <c r="F547" t="s">
+        <v>20</v>
+      </c>
+      <c r="I547">
+        <v>12</v>
+      </c>
+      <c r="J547" t="s">
+        <v>17</v>
+      </c>
+      <c r="N547" t="s">
+        <v>20</v>
+      </c>
+      <c r="O547">
+        <v>1</v>
+      </c>
+      <c r="P547" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="548" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A548" t="s">
+        <v>583</v>
+      </c>
+      <c r="B548">
+        <v>2</v>
+      </c>
+      <c r="C548" t="s">
+        <v>20</v>
+      </c>
+      <c r="D548" t="s">
+        <v>34</v>
+      </c>
+      <c r="E548" t="s">
+        <v>28</v>
+      </c>
+      <c r="F548" t="s">
+        <v>20</v>
+      </c>
+      <c r="G548" t="s">
+        <v>21</v>
+      </c>
+      <c r="I548">
+        <v>6</v>
+      </c>
+      <c r="J548" t="s">
+        <v>17</v>
+      </c>
+      <c r="N548" t="s">
+        <v>20</v>
+      </c>
+      <c r="O548">
+        <v>2</v>
+      </c>
+      <c r="P548" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="549" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A549" t="s">
+        <v>584</v>
+      </c>
+      <c r="B549">
+        <v>2</v>
+      </c>
+      <c r="C549" t="s">
+        <v>17</v>
+      </c>
+      <c r="D549" t="s">
+        <v>34</v>
+      </c>
+      <c r="E549" t="s">
+        <v>25</v>
+      </c>
+      <c r="F549" t="s">
+        <v>20</v>
+      </c>
+      <c r="I549">
+        <v>4</v>
+      </c>
+      <c r="J549" t="s">
+        <v>17</v>
+      </c>
+      <c r="N549" t="s">
+        <v>17</v>
+      </c>
+      <c r="P549" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="550" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A550" t="s">
+        <v>585</v>
+      </c>
+      <c r="B550">
+        <v>2</v>
+      </c>
+      <c r="C550" t="s">
+        <v>17</v>
+      </c>
+      <c r="D550" t="s">
+        <v>34</v>
+      </c>
+      <c r="F550" t="s">
+        <v>17</v>
+      </c>
+      <c r="J550" t="s">
+        <v>20</v>
+      </c>
+      <c r="N550" t="s">
+        <v>20</v>
+      </c>
+      <c r="P550" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="551" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A551" t="s">
+        <v>586</v>
+      </c>
+      <c r="B551">
+        <v>2</v>
+      </c>
+      <c r="C551" t="s">
+        <v>20</v>
+      </c>
+      <c r="D551" t="s">
+        <v>36</v>
+      </c>
+      <c r="E551" t="s">
+        <v>25</v>
+      </c>
+      <c r="F551" t="s">
+        <v>17</v>
+      </c>
+      <c r="J551" t="s">
+        <v>17</v>
+      </c>
+      <c r="N551" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="552" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A552" t="s">
+        <v>587</v>
+      </c>
+      <c r="B552">
+        <v>6</v>
+      </c>
+      <c r="C552" t="s">
+        <v>17</v>
+      </c>
+      <c r="D552" t="s">
+        <v>44</v>
+      </c>
+      <c r="E552" t="s">
+        <v>28</v>
+      </c>
+      <c r="F552" t="s">
+        <v>17</v>
+      </c>
+      <c r="J552" t="s">
+        <v>17</v>
+      </c>
+      <c r="N552" t="s">
+        <v>17</v>
+      </c>
+      <c r="P552" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="553" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A553" t="s">
+        <v>588</v>
+      </c>
+      <c r="B553">
+        <v>2</v>
+      </c>
+      <c r="C553" t="s">
+        <v>20</v>
+      </c>
+      <c r="D553" t="s">
+        <v>44</v>
+      </c>
+      <c r="E553" t="s">
+        <v>28</v>
+      </c>
+      <c r="F553" t="s">
+        <v>17</v>
+      </c>
+      <c r="J553" t="s">
+        <v>20</v>
+      </c>
+      <c r="N553" t="s">
+        <v>17</v>
+      </c>
+      <c r="O553">
+        <v>1</v>
+      </c>
+      <c r="P553" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="554" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A554" t="s">
+        <v>589</v>
+      </c>
+      <c r="B554">
+        <v>2</v>
+      </c>
+      <c r="C554" t="s">
+        <v>17</v>
+      </c>
+      <c r="D554" t="s">
+        <v>44</v>
+      </c>
+      <c r="E554" t="s">
+        <v>25</v>
+      </c>
+      <c r="F554" t="s">
+        <v>17</v>
+      </c>
+      <c r="J554" t="s">
+        <v>17</v>
+      </c>
+      <c r="N554" t="s">
+        <v>20</v>
+      </c>
+      <c r="P554" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="555" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A555" t="s">
+        <v>590</v>
+      </c>
+      <c r="B555">
+        <v>2</v>
+      </c>
+      <c r="C555" t="s">
+        <v>17</v>
+      </c>
+      <c r="D555" t="s">
+        <v>34</v>
+      </c>
+      <c r="E555" t="s">
+        <v>25</v>
+      </c>
+      <c r="F555" t="s">
+        <v>17</v>
+      </c>
+      <c r="J555" t="s">
+        <v>17</v>
+      </c>
+      <c r="N555" t="s">
+        <v>17</v>
+      </c>
+      <c r="P555" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="556" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A556" t="s">
+        <v>591</v>
+      </c>
+      <c r="B556">
+        <v>2</v>
+      </c>
+      <c r="C556" t="s">
+        <v>17</v>
+      </c>
+      <c r="D556" t="s">
+        <v>34</v>
+      </c>
+      <c r="E556" t="s">
+        <v>25</v>
+      </c>
+      <c r="F556" t="s">
+        <v>17</v>
+      </c>
+      <c r="J556" t="s">
+        <v>17</v>
+      </c>
+      <c r="N556" t="s">
+        <v>20</v>
+      </c>
+      <c r="P556" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="557" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A557" t="s">
+        <v>592</v>
+      </c>
+      <c r="B557">
+        <v>2</v>
+      </c>
+      <c r="C557" t="s">
+        <v>17</v>
+      </c>
+      <c r="D557" t="s">
+        <v>18</v>
+      </c>
+      <c r="E557" t="s">
+        <v>25</v>
+      </c>
+      <c r="F557" t="s">
+        <v>20</v>
+      </c>
+      <c r="I557">
+        <v>6</v>
+      </c>
+      <c r="J557" t="s">
+        <v>17</v>
+      </c>
+      <c r="N557" t="s">
+        <v>17</v>
+      </c>
+      <c r="P557" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="558" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A558" t="s">
+        <v>593</v>
+      </c>
+      <c r="B558">
+        <v>2</v>
+      </c>
+      <c r="C558" t="s">
+        <v>17</v>
+      </c>
+      <c r="D558" t="s">
+        <v>32</v>
+      </c>
+      <c r="E558" t="s">
+        <v>28</v>
+      </c>
+      <c r="F558" t="s">
+        <v>17</v>
+      </c>
+      <c r="J558" t="s">
+        <v>17</v>
+      </c>
+      <c r="N558" t="s">
+        <v>17</v>
+      </c>
+      <c r="P558" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="559" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A559" t="s">
+        <v>594</v>
+      </c>
+      <c r="B559">
+        <v>2</v>
+      </c>
+      <c r="C559" t="s">
+        <v>20</v>
+      </c>
+      <c r="D559" t="s">
+        <v>36</v>
+      </c>
+      <c r="E559" t="s">
+        <v>25</v>
+      </c>
+      <c r="F559" t="s">
+        <v>20</v>
+      </c>
+      <c r="I559">
+        <v>7</v>
+      </c>
+      <c r="J559" t="s">
+        <v>17</v>
+      </c>
+      <c r="N559" t="s">
+        <v>17</v>
+      </c>
+      <c r="P559" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="560" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A560" t="s">
+        <v>595</v>
+      </c>
+      <c r="B560">
+        <v>2</v>
+      </c>
+      <c r="C560" t="s">
+        <v>17</v>
+      </c>
+      <c r="D560" t="s">
+        <v>44</v>
+      </c>
+      <c r="E560" t="s">
+        <v>25</v>
+      </c>
+      <c r="F560" t="s">
+        <v>20</v>
+      </c>
+      <c r="G560" t="s">
+        <v>21</v>
+      </c>
+      <c r="I560">
+        <v>7</v>
+      </c>
+      <c r="J560" t="s">
+        <v>17</v>
+      </c>
+      <c r="N560" t="s">
+        <v>20</v>
+      </c>
+      <c r="O560">
+        <v>1</v>
+      </c>
+      <c r="P560" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="561" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A561" t="s">
+        <v>596</v>
+      </c>
+      <c r="B561">
+        <v>1</v>
+      </c>
+      <c r="C561" t="s">
+        <v>17</v>
+      </c>
+      <c r="D561" t="s">
+        <v>44</v>
+      </c>
+      <c r="E561" t="s">
+        <v>19</v>
+      </c>
+      <c r="F561" t="s">
+        <v>17</v>
+      </c>
+      <c r="J561" t="s">
+        <v>17</v>
+      </c>
+      <c r="N561" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="562" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A562" t="s">
+        <v>597</v>
+      </c>
+      <c r="B562">
+        <v>2</v>
+      </c>
+      <c r="C562" t="s">
+        <v>17</v>
+      </c>
+      <c r="D562" t="s">
+        <v>44</v>
+      </c>
+      <c r="E562" t="s">
+        <v>19</v>
+      </c>
+      <c r="F562" t="s">
+        <v>17</v>
+      </c>
+      <c r="J562" t="s">
+        <v>17</v>
+      </c>
+      <c r="N562" t="s">
+        <v>17</v>
+      </c>
+      <c r="O562">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="563" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A563" t="s">
+        <v>598</v>
+      </c>
+      <c r="B563">
+        <v>2</v>
+      </c>
+      <c r="C563" t="s">
+        <v>17</v>
+      </c>
+      <c r="D563" t="s">
+        <v>44</v>
+      </c>
+      <c r="F563" t="s">
+        <v>20</v>
+      </c>
+      <c r="J563" t="s">
+        <v>17</v>
+      </c>
+      <c r="N563" t="s">
+        <v>17</v>
+      </c>
+      <c r="O563">
+        <v>1</v>
+      </c>
+      <c r="P563" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="564" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A564" t="s">
+        <v>599</v>
+      </c>
+      <c r="B564">
+        <v>6</v>
+      </c>
+      <c r="C564" t="s">
+        <v>20</v>
+      </c>
+      <c r="F564" t="s">
+        <v>20</v>
+      </c>
+      <c r="I564">
+        <v>21</v>
+      </c>
+      <c r="J564" t="s">
+        <v>17</v>
+      </c>
+      <c r="N564" t="s">
+        <v>20</v>
+      </c>
+      <c r="O564">
+        <v>1</v>
+      </c>
+      <c r="P564" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="565" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A565" t="s">
+        <v>600</v>
+      </c>
+      <c r="B565">
+        <v>4</v>
+      </c>
+      <c r="C565" t="s">
+        <v>17</v>
+      </c>
+      <c r="D565" t="s">
+        <v>18</v>
+      </c>
+      <c r="E565" t="s">
+        <v>19</v>
+      </c>
+      <c r="F565" t="s">
+        <v>17</v>
+      </c>
+      <c r="J565" t="s">
+        <v>20</v>
+      </c>
+      <c r="M565">
+        <v>3</v>
+      </c>
+      <c r="N565" t="s">
+        <v>17</v>
+      </c>
+      <c r="O565" t="s">
+        <v>48</v>
+      </c>
+      <c r="P565" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="566" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A566" t="s">
+        <v>601</v>
+      </c>
+      <c r="B566">
+        <v>2</v>
+      </c>
+      <c r="C566" t="s">
+        <v>20</v>
+      </c>
+      <c r="D566" t="s">
+        <v>18</v>
+      </c>
+      <c r="E566" t="s">
+        <v>25</v>
+      </c>
+      <c r="F566" t="s">
+        <v>17</v>
+      </c>
+      <c r="J566" t="s">
+        <v>20</v>
+      </c>
+      <c r="N566" t="s">
+        <v>20</v>
+      </c>
+      <c r="O566">
+        <v>1</v>
+      </c>
+      <c r="P566" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="567" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A567" t="s">
+        <v>602</v>
+      </c>
+      <c r="B567">
+        <v>2</v>
+      </c>
+      <c r="C567" t="s">
+        <v>20</v>
+      </c>
+      <c r="F567" t="s">
+        <v>20</v>
+      </c>
+      <c r="I567">
+        <v>9.5</v>
+      </c>
+      <c r="J567" t="s">
+        <v>17</v>
+      </c>
+      <c r="N567" t="s">
+        <v>20</v>
+      </c>
+      <c r="O567">
+        <v>1</v>
+      </c>
+      <c r="P567" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="568" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A568" t="s">
+        <v>603</v>
+      </c>
+      <c r="B568">
+        <v>2</v>
+      </c>
+      <c r="C568" t="s">
+        <v>17</v>
+      </c>
+      <c r="D568" t="s">
+        <v>34</v>
+      </c>
+      <c r="E568" t="s">
+        <v>28</v>
+      </c>
+      <c r="F568" t="s">
+        <v>20</v>
+      </c>
+      <c r="H568" t="s">
+        <v>34</v>
+      </c>
+      <c r="I568">
+        <v>14</v>
+      </c>
+      <c r="J568" t="s">
+        <v>17</v>
+      </c>
+      <c r="N568" t="s">
+        <v>20</v>
+      </c>
+      <c r="O568">
+        <v>1</v>
+      </c>
+      <c r="P568" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="569" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A569" t="s">
+        <v>604</v>
+      </c>
+      <c r="B569">
+        <v>2</v>
+      </c>
+      <c r="C569" t="s">
+        <v>17</v>
+      </c>
+      <c r="D569" t="s">
+        <v>34</v>
+      </c>
+      <c r="E569" t="s">
+        <v>28</v>
+      </c>
+      <c r="F569" t="s">
+        <v>20</v>
+      </c>
+      <c r="I569">
+        <v>6</v>
+      </c>
+      <c r="J569" t="s">
+        <v>17</v>
+      </c>
+      <c r="N569" t="s">
+        <v>20</v>
+      </c>
+      <c r="P569" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="570" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A570" t="s">
+        <v>605</v>
+      </c>
+      <c r="B570">
+        <v>2</v>
+      </c>
+      <c r="C570" t="s">
+        <v>20</v>
+      </c>
+      <c r="D570" t="s">
+        <v>44</v>
+      </c>
+      <c r="E570" t="s">
+        <v>25</v>
+      </c>
+      <c r="F570" t="s">
+        <v>20</v>
+      </c>
+      <c r="I570">
+        <v>5</v>
+      </c>
+      <c r="J570" t="s">
+        <v>17</v>
+      </c>
+      <c r="N570" t="s">
+        <v>20</v>
+      </c>
+      <c r="O570" t="s">
+        <v>52</v>
+      </c>
+      <c r="P570" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="571" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A571" t="s">
+        <v>606</v>
+      </c>
+      <c r="B571">
+        <v>2</v>
+      </c>
+      <c r="C571" t="s">
+        <v>17</v>
+      </c>
+      <c r="D571" t="s">
+        <v>32</v>
+      </c>
+      <c r="E571" t="s">
+        <v>25</v>
+      </c>
+      <c r="F571" t="s">
+        <v>17</v>
+      </c>
+      <c r="J571" t="s">
+        <v>17</v>
+      </c>
+      <c r="N571" t="s">
+        <v>17</v>
+      </c>
+      <c r="P571" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="572" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A572" t="s">
+        <v>607</v>
+      </c>
+      <c r="B572">
+        <v>2</v>
+      </c>
+      <c r="C572" t="s">
+        <v>17</v>
+      </c>
+      <c r="D572" t="s">
+        <v>18</v>
+      </c>
+      <c r="E572" t="s">
+        <v>28</v>
+      </c>
+      <c r="F572" t="s">
+        <v>20</v>
+      </c>
+      <c r="J572" t="s">
+        <v>17</v>
+      </c>
+      <c r="N572" t="s">
+        <v>20</v>
+      </c>
+      <c r="O572">
+        <v>1</v>
+      </c>
+      <c r="P572" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="573" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A573" t="s">
+        <v>608</v>
+      </c>
+      <c r="B573">
+        <v>4</v>
+      </c>
+      <c r="C573" t="s">
+        <v>17</v>
+      </c>
+      <c r="D573" t="s">
+        <v>44</v>
+      </c>
+      <c r="F573" t="s">
+        <v>20</v>
+      </c>
+      <c r="I573">
+        <v>7</v>
+      </c>
+      <c r="J573" t="s">
+        <v>17</v>
+      </c>
+      <c r="N573" t="s">
+        <v>17</v>
+      </c>
+      <c r="O573">
+        <v>3</v>
+      </c>
+      <c r="P573" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="574" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A574" t="s">
+        <v>609</v>
+      </c>
+      <c r="B574">
+        <v>6</v>
+      </c>
+      <c r="C574" t="s">
+        <v>17</v>
+      </c>
+      <c r="F574" t="s">
+        <v>20</v>
+      </c>
+      <c r="I574">
+        <v>10</v>
+      </c>
+      <c r="J574" t="s">
+        <v>17</v>
+      </c>
+      <c r="N574" t="s">
+        <v>20</v>
+      </c>
+      <c r="P574" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="575" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A575" t="s">
+        <v>610</v>
+      </c>
+      <c r="B575">
+        <v>2</v>
+      </c>
+      <c r="C575" t="s">
+        <v>17</v>
+      </c>
+      <c r="D575" t="s">
+        <v>34</v>
+      </c>
+      <c r="E575" t="s">
+        <v>25</v>
+      </c>
+      <c r="F575" t="s">
+        <v>17</v>
+      </c>
+      <c r="J575" t="s">
+        <v>17</v>
+      </c>
+      <c r="N575" t="s">
+        <v>20</v>
+      </c>
+      <c r="P575" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="576" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A576" t="s">
+        <v>611</v>
+      </c>
+      <c r="B576">
+        <v>1</v>
+      </c>
+      <c r="C576" t="s">
+        <v>20</v>
+      </c>
+      <c r="D576" t="s">
+        <v>44</v>
+      </c>
+      <c r="E576" t="s">
+        <v>28</v>
+      </c>
+      <c r="F576" t="s">
+        <v>17</v>
+      </c>
+      <c r="J576" t="s">
+        <v>17</v>
+      </c>
+      <c r="N576" t="s">
+        <v>17</v>
+      </c>
+      <c r="P576" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="577" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A577" t="s">
+        <v>612</v>
+      </c>
+      <c r="B577">
+        <v>2</v>
+      </c>
+      <c r="C577" t="s">
+        <v>20</v>
+      </c>
+      <c r="D577" t="s">
+        <v>32</v>
+      </c>
+      <c r="E577" t="s">
+        <v>25</v>
+      </c>
+      <c r="F577" t="s">
+        <v>17</v>
+      </c>
+      <c r="J577" t="s">
+        <v>17</v>
+      </c>
+      <c r="N577" t="s">
+        <v>20</v>
+      </c>
+      <c r="P577" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="578" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A578" t="s">
+        <v>613</v>
+      </c>
+      <c r="B578">
+        <v>1</v>
+      </c>
+      <c r="C578" t="s">
+        <v>17</v>
+      </c>
+      <c r="D578" t="s">
+        <v>34</v>
+      </c>
+      <c r="F578" t="s">
+        <v>17</v>
+      </c>
+      <c r="J578" t="s">
+        <v>17</v>
+      </c>
+      <c r="N578" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="579" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A579" t="s">
+        <v>614</v>
+      </c>
+      <c r="B579">
+        <v>5</v>
+      </c>
+      <c r="C579" t="s">
+        <v>20</v>
+      </c>
+      <c r="F579" t="s">
+        <v>20</v>
+      </c>
+      <c r="G579" t="s">
+        <v>79</v>
+      </c>
+      <c r="H579" t="s">
+        <v>42</v>
+      </c>
+      <c r="I579">
+        <v>42</v>
+      </c>
+      <c r="J579" t="s">
+        <v>17</v>
+      </c>
+      <c r="N579" t="s">
+        <v>17</v>
+      </c>
+      <c r="O579">
+        <v>3</v>
+      </c>
+      <c r="P579" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="580" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A580" t="s">
+        <v>615</v>
+      </c>
+      <c r="B580">
+        <v>2</v>
+      </c>
+      <c r="C580" t="s">
+        <v>17</v>
+      </c>
+      <c r="D580" t="s">
+        <v>34</v>
+      </c>
+      <c r="E580" t="s">
+        <v>25</v>
+      </c>
+      <c r="F580" t="s">
+        <v>17</v>
+      </c>
+      <c r="J580" t="s">
+        <v>20</v>
+      </c>
+      <c r="N580" t="s">
+        <v>20</v>
+      </c>
+      <c r="P580" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="581" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A581" t="s">
+        <v>616</v>
+      </c>
+      <c r="B581">
+        <v>2</v>
+      </c>
+      <c r="C581" t="s">
+        <v>20</v>
+      </c>
+      <c r="F581" t="s">
+        <v>17</v>
+      </c>
+      <c r="J581" t="s">
+        <v>17</v>
+      </c>
+      <c r="N581" t="s">
+        <v>17</v>
+      </c>
+      <c r="P581" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="582" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A582" t="s">
+        <v>617</v>
+      </c>
+      <c r="B582">
+        <v>6</v>
+      </c>
+      <c r="C582" t="s">
+        <v>20</v>
+      </c>
+      <c r="D582" t="s">
+        <v>55</v>
+      </c>
+      <c r="F582" t="s">
+        <v>20</v>
+      </c>
+      <c r="H582" t="s">
+        <v>42</v>
+      </c>
+      <c r="I582">
+        <v>24</v>
+      </c>
+      <c r="J582" t="s">
+        <v>17</v>
+      </c>
+      <c r="N582" t="s">
+        <v>17</v>
+      </c>
+      <c r="P582" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="583" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A583" t="s">
+        <v>618</v>
+      </c>
+      <c r="B583">
+        <v>2</v>
+      </c>
+      <c r="C583" t="s">
+        <v>17</v>
+      </c>
+      <c r="D583" t="s">
+        <v>44</v>
+      </c>
+      <c r="E583" t="s">
+        <v>28</v>
+      </c>
+      <c r="F583" t="s">
+        <v>17</v>
+      </c>
+      <c r="J583" t="s">
+        <v>17</v>
+      </c>
+      <c r="N583" t="s">
+        <v>20</v>
+      </c>
+      <c r="P583" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="584" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A584" t="s">
+        <v>619</v>
+      </c>
+      <c r="B584">
+        <v>2</v>
+      </c>
+      <c r="C584" t="s">
+        <v>17</v>
+      </c>
+      <c r="D584" t="s">
+        <v>34</v>
+      </c>
+      <c r="F584" t="s">
+        <v>17</v>
+      </c>
+      <c r="J584" t="s">
+        <v>17</v>
+      </c>
+      <c r="N584" t="s">
+        <v>20</v>
+      </c>
+      <c r="P584" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="585" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A585" t="s">
+        <v>620</v>
+      </c>
+      <c r="B585">
+        <v>6</v>
+      </c>
+      <c r="C585" t="s">
+        <v>17</v>
+      </c>
+      <c r="F585" t="s">
+        <v>20</v>
+      </c>
+      <c r="H585" t="s">
+        <v>34</v>
+      </c>
+      <c r="I585">
+        <v>8</v>
+      </c>
+      <c r="J585" t="s">
+        <v>17</v>
+      </c>
+      <c r="N585" t="s">
+        <v>17</v>
+      </c>
+      <c r="P585" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="586" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A586" t="s">
+        <v>621</v>
+      </c>
+      <c r="B586">
+        <v>4</v>
+      </c>
+      <c r="C586" t="s">
+        <v>20</v>
+      </c>
+      <c r="D586" t="s">
+        <v>32</v>
+      </c>
+      <c r="E586" t="s">
+        <v>28</v>
+      </c>
+      <c r="F586" t="s">
+        <v>20</v>
+      </c>
+      <c r="G586" t="s">
+        <v>21</v>
+      </c>
+      <c r="I586">
+        <v>7</v>
+      </c>
+      <c r="J586" t="s">
+        <v>20</v>
+      </c>
+      <c r="M586">
+        <v>21</v>
+      </c>
+      <c r="N586" t="s">
+        <v>17</v>
+      </c>
+      <c r="O586" t="s">
+        <v>22</v>
+      </c>
+      <c r="P586" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="587" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A587" t="s">
+        <v>622</v>
+      </c>
+      <c r="B587">
+        <v>2</v>
+      </c>
+      <c r="C587" t="s">
+        <v>17</v>
+      </c>
+      <c r="D587" t="s">
+        <v>32</v>
+      </c>
+      <c r="E587" t="s">
+        <v>25</v>
+      </c>
+      <c r="F587" t="s">
+        <v>17</v>
+      </c>
+      <c r="J587" t="s">
+        <v>17</v>
+      </c>
+      <c r="N587" t="s">
+        <v>20</v>
+      </c>
+      <c r="P587" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="588" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A588" t="s">
+        <v>623</v>
+      </c>
+      <c r="B588">
+        <v>4</v>
+      </c>
+      <c r="C588" t="s">
+        <v>20</v>
+      </c>
+      <c r="F588" t="s">
+        <v>17</v>
+      </c>
+      <c r="J588" t="s">
+        <v>20</v>
+      </c>
+      <c r="N588" t="s">
+        <v>17</v>
+      </c>
+      <c r="P588" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="589" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A589" t="s">
+        <v>624</v>
+      </c>
+      <c r="B589">
+        <v>4</v>
+      </c>
+      <c r="C589" t="s">
+        <v>17</v>
+      </c>
+      <c r="D589" t="s">
+        <v>18</v>
+      </c>
+      <c r="F589" t="s">
+        <v>20</v>
+      </c>
+      <c r="I589">
+        <v>6</v>
+      </c>
+      <c r="J589" t="s">
+        <v>17</v>
+      </c>
+      <c r="N589" t="s">
+        <v>20</v>
+      </c>
+      <c r="O589">
+        <v>3</v>
+      </c>
+      <c r="P589" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="590" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A590" t="s">
+        <v>625</v>
+      </c>
+      <c r="B590">
+        <v>4</v>
+      </c>
+      <c r="C590" t="s">
+        <v>17</v>
+      </c>
+      <c r="D590" t="s">
+        <v>18</v>
+      </c>
+      <c r="E590" t="s">
+        <v>30</v>
+      </c>
+      <c r="F590" t="s">
+        <v>20</v>
+      </c>
+      <c r="H590" t="s">
+        <v>42</v>
+      </c>
+      <c r="I590">
+        <v>10</v>
+      </c>
+      <c r="J590" t="s">
+        <v>17</v>
+      </c>
+      <c r="N590" t="s">
+        <v>20</v>
+      </c>
+      <c r="O590">
+        <v>3</v>
+      </c>
+      <c r="P590" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="591" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A591" t="s">
+        <v>626</v>
+      </c>
+      <c r="B591">
+        <v>2</v>
+      </c>
+      <c r="C591" t="s">
+        <v>20</v>
+      </c>
+      <c r="D591" t="s">
+        <v>34</v>
+      </c>
+      <c r="E591" t="s">
+        <v>25</v>
+      </c>
+      <c r="F591" t="s">
+        <v>17</v>
+      </c>
+      <c r="J591" t="s">
+        <v>17</v>
+      </c>
+      <c r="N591" t="s">
+        <v>17</v>
+      </c>
+      <c r="P591" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="592" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A592" t="s">
+        <v>627</v>
+      </c>
+      <c r="B592">
+        <v>2</v>
+      </c>
+      <c r="C592" t="s">
+        <v>17</v>
+      </c>
+      <c r="D592" t="s">
+        <v>34</v>
+      </c>
+      <c r="E592" t="s">
+        <v>25</v>
+      </c>
+      <c r="F592" t="s">
+        <v>17</v>
+      </c>
+      <c r="J592" t="s">
+        <v>17</v>
+      </c>
+      <c r="N592" t="s">
+        <v>17</v>
+      </c>
+      <c r="P592" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="593" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A593" t="s">
+        <v>628</v>
+      </c>
+      <c r="B593">
+        <v>6</v>
+      </c>
+      <c r="C593" t="s">
+        <v>17</v>
+      </c>
+      <c r="D593" t="s">
+        <v>18</v>
+      </c>
+      <c r="F593" t="s">
+        <v>17</v>
+      </c>
+      <c r="J593" t="s">
+        <v>20</v>
+      </c>
+      <c r="M593">
+        <v>30</v>
+      </c>
+      <c r="N593" t="s">
+        <v>17</v>
+      </c>
+      <c r="O593" t="s">
+        <v>52</v>
+      </c>
+      <c r="P593" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="594" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A594" t="s">
+        <v>629</v>
+      </c>
+      <c r="B594">
+        <v>4</v>
+      </c>
+      <c r="C594" t="s">
+        <v>17</v>
+      </c>
+      <c r="D594" t="s">
+        <v>18</v>
+      </c>
+      <c r="E594" t="s">
+        <v>19</v>
+      </c>
+      <c r="F594" t="s">
+        <v>17</v>
+      </c>
+      <c r="J594" t="s">
+        <v>20</v>
+      </c>
+      <c r="M594">
+        <v>44</v>
+      </c>
+      <c r="N594" t="s">
+        <v>20</v>
+      </c>
+      <c r="O594">
+        <v>2</v>
+      </c>
+      <c r="P594" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="595" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A595" t="s">
+        <v>630</v>
+      </c>
+      <c r="B595">
+        <v>2</v>
+      </c>
+      <c r="C595" t="s">
+        <v>17</v>
+      </c>
+      <c r="D595" t="s">
+        <v>44</v>
+      </c>
+      <c r="E595" t="s">
+        <v>28</v>
+      </c>
+      <c r="F595" t="s">
+        <v>17</v>
+      </c>
+      <c r="J595" t="s">
+        <v>17</v>
+      </c>
+      <c r="N595" t="s">
+        <v>20</v>
+      </c>
+      <c r="P595" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="596" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A596" t="s">
+        <v>631</v>
+      </c>
+      <c r="B596">
+        <v>2</v>
+      </c>
+      <c r="C596" t="s">
+        <v>17</v>
+      </c>
+      <c r="D596" t="s">
+        <v>44</v>
+      </c>
+      <c r="E596" t="s">
+        <v>28</v>
+      </c>
+      <c r="F596" t="s">
+        <v>17</v>
+      </c>
+      <c r="J596" t="s">
+        <v>17</v>
+      </c>
+      <c r="N596" t="s">
+        <v>20</v>
+      </c>
+      <c r="P596" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="597" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A597" t="s">
+        <v>632</v>
+      </c>
+      <c r="B597">
+        <v>2</v>
+      </c>
+      <c r="C597" t="s">
+        <v>17</v>
+      </c>
+      <c r="D597" t="s">
+        <v>44</v>
+      </c>
+      <c r="E597" t="s">
+        <v>25</v>
+      </c>
+      <c r="F597" t="s">
+        <v>17</v>
+      </c>
+      <c r="J597" t="s">
+        <v>17</v>
+      </c>
+      <c r="N597" t="s">
+        <v>20</v>
+      </c>
+      <c r="P597" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="598" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A598" t="s">
+        <v>633</v>
+      </c>
+      <c r="B598">
+        <v>2</v>
+      </c>
+      <c r="C598" t="s">
+        <v>20</v>
+      </c>
+      <c r="F598" t="s">
+        <v>17</v>
+      </c>
+      <c r="J598" t="s">
+        <v>17</v>
+      </c>
+      <c r="N598" t="s">
+        <v>17</v>
+      </c>
+      <c r="P598" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="599" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A599" t="s">
+        <v>634</v>
+      </c>
+      <c r="B599">
+        <v>2</v>
+      </c>
+      <c r="C599" t="s">
+        <v>17</v>
+      </c>
+      <c r="D599" t="s">
+        <v>36</v>
+      </c>
+      <c r="E599" t="s">
+        <v>25</v>
+      </c>
+      <c r="F599" t="s">
+        <v>20</v>
+      </c>
+      <c r="I599">
+        <v>4</v>
+      </c>
+      <c r="J599" t="s">
+        <v>17</v>
+      </c>
+      <c r="N599" t="s">
+        <v>17</v>
+      </c>
+      <c r="P599" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="600" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A600" t="s">
+        <v>635</v>
+      </c>
+      <c r="B600">
+        <v>2</v>
+      </c>
+      <c r="C600" t="s">
+        <v>20</v>
+      </c>
+      <c r="D600" t="s">
+        <v>55</v>
+      </c>
+      <c r="E600" t="s">
+        <v>25</v>
+      </c>
+      <c r="F600" t="s">
+        <v>17</v>
+      </c>
+      <c r="J600" t="s">
+        <v>17</v>
+      </c>
+      <c r="N600" t="s">
+        <v>20</v>
+      </c>
+      <c r="P600" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="601" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A601" t="s">
+        <v>636</v>
+      </c>
+      <c r="B601">
+        <v>2</v>
+      </c>
+      <c r="C601" t="s">
+        <v>17</v>
+      </c>
+      <c r="D601" t="s">
+        <v>34</v>
+      </c>
+      <c r="E601" t="s">
+        <v>28</v>
+      </c>
+      <c r="F601" t="s">
+        <v>20</v>
+      </c>
+      <c r="J601" t="s">
+        <v>17</v>
+      </c>
+      <c r="N601" t="s">
+        <v>20</v>
+      </c>
+      <c r="P601" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="602" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A602" t="s">
+        <v>637</v>
+      </c>
+      <c r="B602">
+        <v>2</v>
+      </c>
+      <c r="C602" t="s">
+        <v>20</v>
+      </c>
+      <c r="F602" t="s">
+        <v>17</v>
+      </c>
+      <c r="J602" t="s">
+        <v>17</v>
+      </c>
+      <c r="N602" t="s">
+        <v>20</v>
+      </c>
+      <c r="O602" t="s">
+        <v>52</v>
+      </c>
+      <c r="P602" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="603" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A603" t="s">
+        <v>638</v>
+      </c>
+      <c r="B603">
+        <v>6</v>
+      </c>
+      <c r="C603" t="s">
+        <v>20</v>
+      </c>
+      <c r="D603" t="s">
+        <v>32</v>
+      </c>
+      <c r="F603" t="s">
+        <v>17</v>
+      </c>
+      <c r="J603" t="s">
+        <v>20</v>
+      </c>
+      <c r="M603">
+        <v>4</v>
+      </c>
+      <c r="N603" t="s">
+        <v>17</v>
+      </c>
+      <c r="O603">
+        <v>1</v>
+      </c>
+      <c r="P603" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="604" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A604" t="s">
+        <v>639</v>
+      </c>
+      <c r="B604">
+        <v>2</v>
+      </c>
+      <c r="C604" t="s">
+        <v>20</v>
+      </c>
+      <c r="D604" t="s">
+        <v>18</v>
+      </c>
+      <c r="E604" t="s">
+        <v>30</v>
+      </c>
+      <c r="F604" t="s">
+        <v>20</v>
+      </c>
+      <c r="G604" t="s">
+        <v>21</v>
+      </c>
+      <c r="I604">
+        <v>6.7</v>
+      </c>
+      <c r="J604" t="s">
+        <v>17</v>
+      </c>
+      <c r="N604" t="s">
+        <v>20</v>
+      </c>
+      <c r="O604">
+        <v>1</v>
+      </c>
+      <c r="P604" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="605" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A605" t="s">
+        <v>640</v>
+      </c>
+      <c r="B605">
+        <v>4</v>
+      </c>
+      <c r="C605" t="s">
+        <v>17</v>
+      </c>
+      <c r="D605" t="s">
+        <v>34</v>
+      </c>
+      <c r="F605" t="s">
+        <v>17</v>
+      </c>
+      <c r="J605" t="s">
+        <v>20</v>
+      </c>
+      <c r="M605">
+        <v>22</v>
+      </c>
+      <c r="N605" t="s">
+        <v>17</v>
+      </c>
+      <c r="O605">
+        <v>3</v>
+      </c>
+      <c r="P605" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="606" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A606" t="s">
+        <v>641</v>
+      </c>
+      <c r="B606">
+        <v>2</v>
+      </c>
+      <c r="C606" t="s">
+        <v>17</v>
+      </c>
+      <c r="D606" t="s">
+        <v>34</v>
+      </c>
+      <c r="E606" t="s">
+        <v>25</v>
+      </c>
+      <c r="F606" t="s">
+        <v>20</v>
+      </c>
+      <c r="H606" t="s">
+        <v>34</v>
+      </c>
+      <c r="I606">
+        <v>13</v>
+      </c>
+      <c r="J606" t="s">
+        <v>17</v>
+      </c>
+      <c r="N606" t="s">
+        <v>20</v>
+      </c>
+      <c r="O606">
+        <v>1</v>
+      </c>
+      <c r="P606" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="607" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A607" t="s">
+        <v>642</v>
+      </c>
+      <c r="B607">
+        <v>2</v>
+      </c>
+      <c r="C607" t="s">
+        <v>17</v>
+      </c>
+      <c r="F607" t="s">
+        <v>17</v>
+      </c>
+      <c r="J607" t="s">
+        <v>17</v>
+      </c>
+      <c r="N607" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="608" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A608" t="s">
+        <v>643</v>
+      </c>
+      <c r="B608">
+        <v>4</v>
+      </c>
+      <c r="C608" t="s">
+        <v>17</v>
+      </c>
+      <c r="D608" t="s">
+        <v>27</v>
+      </c>
+      <c r="E608" t="s">
+        <v>25</v>
+      </c>
+      <c r="F608" t="s">
+        <v>17</v>
+      </c>
+      <c r="J608" t="s">
+        <v>20</v>
+      </c>
+      <c r="M608">
+        <v>10</v>
+      </c>
+      <c r="N608" t="s">
+        <v>20</v>
+      </c>
+      <c r="O608" t="s">
+        <v>48</v>
+      </c>
+      <c r="P608" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="609" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A609" t="s">
+        <v>644</v>
+      </c>
+      <c r="B609">
+        <v>2</v>
+      </c>
+      <c r="C609" t="s">
+        <v>17</v>
+      </c>
+      <c r="D609" t="s">
+        <v>18</v>
+      </c>
+      <c r="E609" t="s">
+        <v>25</v>
+      </c>
+      <c r="F609" t="s">
+        <v>17</v>
+      </c>
+      <c r="J609" t="s">
+        <v>17</v>
+      </c>
+      <c r="N609" t="s">
+        <v>17</v>
+      </c>
+      <c r="P609" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="610" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A610" t="s">
+        <v>645</v>
+      </c>
+      <c r="B610">
+        <v>2</v>
+      </c>
+      <c r="C610" t="s">
+        <v>17</v>
+      </c>
+      <c r="E610" t="s">
+        <v>25</v>
+      </c>
+      <c r="F610" t="s">
+        <v>20</v>
+      </c>
+      <c r="I610">
+        <v>13</v>
+      </c>
+      <c r="J610" t="s">
+        <v>17</v>
+      </c>
+      <c r="N610" t="s">
+        <v>20</v>
+      </c>
+      <c r="P610" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="611" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A611" t="s">
+        <v>646</v>
+      </c>
+      <c r="B611">
+        <v>2</v>
+      </c>
+      <c r="C611" t="s">
+        <v>17</v>
+      </c>
+      <c r="D611" t="s">
+        <v>44</v>
+      </c>
+      <c r="E611" t="s">
+        <v>30</v>
+      </c>
+      <c r="F611" t="s">
+        <v>20</v>
+      </c>
+      <c r="I611">
+        <v>10</v>
+      </c>
+      <c r="J611" t="s">
+        <v>17</v>
+      </c>
+      <c r="N611" t="s">
+        <v>20</v>
+      </c>
+      <c r="O611">
+        <v>2</v>
+      </c>
+      <c r="P611" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="612" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A612" t="s">
+        <v>647</v>
+      </c>
+      <c r="B612">
+        <v>2</v>
+      </c>
+      <c r="C612" t="s">
+        <v>20</v>
+      </c>
+      <c r="D612" t="s">
+        <v>34</v>
+      </c>
+      <c r="E612" t="s">
+        <v>25</v>
+      </c>
+      <c r="F612" t="s">
+        <v>17</v>
+      </c>
+      <c r="J612" t="s">
+        <v>17</v>
+      </c>
+      <c r="N612" t="s">
+        <v>17</v>
+      </c>
+      <c r="P612" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="613" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A613" t="s">
+        <v>648</v>
+      </c>
+      <c r="B613">
+        <v>2</v>
+      </c>
+      <c r="C613" t="s">
+        <v>17</v>
+      </c>
+      <c r="D613" t="s">
+        <v>32</v>
+      </c>
+      <c r="F613" t="s">
+        <v>20</v>
+      </c>
+      <c r="I613">
+        <v>6</v>
+      </c>
+      <c r="J613" t="s">
+        <v>20</v>
+      </c>
+      <c r="N613" t="s">
+        <v>17</v>
+      </c>
+      <c r="O613">
+        <v>1</v>
+      </c>
+      <c r="P613" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="614" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A614" t="s">
+        <v>649</v>
+      </c>
+      <c r="B614">
+        <v>2</v>
+      </c>
+      <c r="C614" t="s">
+        <v>17</v>
+      </c>
+      <c r="D614" t="s">
+        <v>44</v>
+      </c>
+      <c r="F614" t="s">
+        <v>20</v>
+      </c>
+      <c r="G614" t="s">
+        <v>21</v>
+      </c>
+      <c r="H614" t="s">
+        <v>34</v>
+      </c>
+      <c r="I614">
+        <v>12</v>
+      </c>
+      <c r="J614" t="s">
+        <v>17</v>
+      </c>
+      <c r="N614" t="s">
+        <v>17</v>
+      </c>
+      <c r="O614">
+        <v>1</v>
+      </c>
+      <c r="P614" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="615" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A615" t="s">
+        <v>650</v>
+      </c>
+      <c r="B615">
+        <v>2</v>
+      </c>
+      <c r="C615" t="s">
+        <v>20</v>
+      </c>
+      <c r="D615" t="s">
+        <v>32</v>
+      </c>
+      <c r="E615" t="s">
+        <v>28</v>
+      </c>
+      <c r="F615" t="s">
+        <v>20</v>
+      </c>
+      <c r="I615">
+        <v>10</v>
+      </c>
+      <c r="J615" t="s">
+        <v>17</v>
+      </c>
+      <c r="N615" t="s">
+        <v>17</v>
+      </c>
+      <c r="O615" t="s">
+        <v>52</v>
+      </c>
+      <c r="P615" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="616" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A616" t="s">
+        <v>651</v>
+      </c>
+      <c r="B616">
+        <v>2</v>
+      </c>
+      <c r="C616" t="s">
+        <v>20</v>
+      </c>
+      <c r="D616" t="s">
+        <v>32</v>
+      </c>
+      <c r="F616" t="s">
+        <v>17</v>
+      </c>
+      <c r="J616" t="s">
+        <v>17</v>
+      </c>
+      <c r="N616" t="s">
+        <v>20</v>
+      </c>
+      <c r="P616" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="617" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A617" t="s">
+        <v>652</v>
+      </c>
+      <c r="B617">
+        <v>2</v>
+      </c>
+      <c r="C617" t="s">
+        <v>20</v>
+      </c>
+      <c r="D617" t="s">
+        <v>34</v>
+      </c>
+      <c r="E617" t="s">
+        <v>25</v>
+      </c>
+      <c r="F617" t="s">
+        <v>17</v>
+      </c>
+      <c r="J617" t="s">
+        <v>17</v>
+      </c>
+      <c r="N617" t="s">
+        <v>17</v>
+      </c>
+      <c r="P617" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="618" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A618" t="s">
+        <v>653</v>
+      </c>
+      <c r="B618">
+        <v>2</v>
+      </c>
+      <c r="C618" t="s">
+        <v>20</v>
+      </c>
+      <c r="D618" t="s">
+        <v>34</v>
+      </c>
+      <c r="F618" t="s">
+        <v>17</v>
+      </c>
+      <c r="J618" t="s">
+        <v>17</v>
+      </c>
+      <c r="N618" t="s">
+        <v>20</v>
+      </c>
+      <c r="P618" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="619" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A619" t="s">
+        <v>654</v>
+      </c>
+      <c r="B619">
+        <v>2</v>
+      </c>
+      <c r="C619" t="s">
+        <v>20</v>
+      </c>
+      <c r="D619" t="s">
+        <v>36</v>
+      </c>
+      <c r="E619" t="s">
+        <v>28</v>
+      </c>
+      <c r="F619" t="s">
+        <v>20</v>
+      </c>
+      <c r="H619" t="s">
+        <v>42</v>
+      </c>
+      <c r="J619" t="s">
+        <v>17</v>
+      </c>
+      <c r="N619" t="s">
+        <v>20</v>
+      </c>
+      <c r="P619" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="620" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A620" t="s">
+        <v>655</v>
+      </c>
+      <c r="B620">
+        <v>2</v>
+      </c>
+      <c r="C620" t="s">
+        <v>20</v>
+      </c>
+      <c r="D620" t="s">
+        <v>55</v>
+      </c>
+      <c r="F620" t="s">
+        <v>17</v>
+      </c>
+      <c r="J620" t="s">
+        <v>17</v>
+      </c>
+      <c r="N620" t="s">
+        <v>20</v>
+      </c>
+      <c r="P620" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="621" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A621" t="s">
+        <v>656</v>
+      </c>
+      <c r="B621">
+        <v>5</v>
+      </c>
+      <c r="C621" t="s">
+        <v>17</v>
+      </c>
+      <c r="D621" t="s">
+        <v>18</v>
+      </c>
+      <c r="F621" t="s">
+        <v>20</v>
+      </c>
+      <c r="G621" t="s">
+        <v>79</v>
+      </c>
+      <c r="H621" t="s">
+        <v>42</v>
+      </c>
+      <c r="I621">
+        <v>14</v>
+      </c>
+      <c r="J621" t="s">
+        <v>20</v>
+      </c>
+      <c r="M621">
+        <v>21</v>
+      </c>
+      <c r="N621" t="s">
+        <v>17</v>
+      </c>
+      <c r="O621">
+        <v>3</v>
+      </c>
+      <c r="P621" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="622" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A622" t="s">
+        <v>657</v>
+      </c>
+      <c r="B622">
+        <v>2</v>
+      </c>
+      <c r="C622" t="s">
+        <v>17</v>
+      </c>
+      <c r="D622" t="s">
+        <v>55</v>
+      </c>
+      <c r="F622" t="s">
+        <v>17</v>
+      </c>
+      <c r="J622" t="s">
+        <v>17</v>
+      </c>
+      <c r="N622" t="s">
+        <v>17</v>
+      </c>
+      <c r="P622" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="623" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A623" t="s">
+        <v>658</v>
+      </c>
+      <c r="B623">
+        <v>6</v>
+      </c>
+      <c r="C623" t="s">
+        <v>17</v>
+      </c>
+      <c r="D623" t="s">
+        <v>44</v>
+      </c>
+      <c r="F623" t="s">
+        <v>17</v>
+      </c>
+      <c r="J623" t="s">
+        <v>17</v>
+      </c>
+      <c r="N623" t="s">
+        <v>17</v>
+      </c>
+      <c r="O623">
+        <v>1</v>
+      </c>
+      <c r="P623" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="624" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A624" t="s">
+        <v>659</v>
+      </c>
+      <c r="B624">
+        <v>6</v>
+      </c>
+      <c r="C624" t="s">
+        <v>17</v>
+      </c>
+      <c r="D624" t="s">
+        <v>36</v>
+      </c>
+      <c r="F624" t="s">
+        <v>20</v>
+      </c>
+      <c r="G624" t="s">
+        <v>79</v>
+      </c>
+      <c r="I624">
+        <v>31</v>
+      </c>
+      <c r="J624" t="s">
+        <v>20</v>
+      </c>
+      <c r="N624" t="s">
+        <v>17</v>
+      </c>
+      <c r="O624">
+        <v>3</v>
+      </c>
+      <c r="P624" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="625" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A625" t="s">
+        <v>660</v>
+      </c>
+      <c r="B625">
+        <v>0</v>
+      </c>
+      <c r="C625" t="s">
+        <v>20</v>
+      </c>
+      <c r="D625" t="s">
+        <v>32</v>
+      </c>
+      <c r="F625" t="s">
+        <v>20</v>
+      </c>
+      <c r="J625" t="s">
+        <v>17</v>
+      </c>
+      <c r="N625" t="s">
+        <v>17</v>
+      </c>
+      <c r="O625">
+        <v>3</v>
+      </c>
+      <c r="P625" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="626" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A626" t="s">
+        <v>661</v>
+      </c>
+      <c r="B626">
+        <v>2</v>
+      </c>
+      <c r="C626" t="s">
+        <v>17</v>
+      </c>
+      <c r="F626" t="s">
+        <v>17</v>
+      </c>
+      <c r="J626" t="s">
+        <v>17</v>
+      </c>
+      <c r="N626" t="s">
+        <v>17</v>
+      </c>
+      <c r="O626">
+        <v>1</v>
+      </c>
+      <c r="P626" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="627" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A627" t="s">
+        <v>662</v>
+      </c>
+      <c r="B627">
+        <v>4</v>
+      </c>
+      <c r="C627" t="s">
+        <v>17</v>
+      </c>
+      <c r="D627" t="s">
+        <v>34</v>
+      </c>
+      <c r="E627" t="s">
+        <v>19</v>
+      </c>
+      <c r="F627" t="s">
+        <v>17</v>
+      </c>
+      <c r="J627" t="s">
+        <v>20</v>
+      </c>
+      <c r="M627">
+        <v>39</v>
+      </c>
+      <c r="N627" t="s">
+        <v>17</v>
+      </c>
+      <c r="O627">
+        <v>3</v>
+      </c>
+      <c r="P627" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="628" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A628" t="s">
+        <v>663</v>
+      </c>
+      <c r="B628">
+        <v>2</v>
+      </c>
+      <c r="C628" t="s">
+        <v>20</v>
+      </c>
+      <c r="F628" t="s">
+        <v>17</v>
+      </c>
+      <c r="J628" t="s">
+        <v>17</v>
+      </c>
+      <c r="N628" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="629" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A629" t="s">
+        <v>664</v>
+      </c>
+      <c r="B629">
+        <v>2</v>
+      </c>
+      <c r="C629" t="s">
+        <v>20</v>
+      </c>
+      <c r="D629" t="s">
+        <v>44</v>
+      </c>
+      <c r="E629" t="s">
+        <v>25</v>
+      </c>
+      <c r="F629" t="s">
+        <v>17</v>
+      </c>
+      <c r="J629" t="s">
+        <v>17</v>
+      </c>
+      <c r="N629" t="s">
+        <v>20</v>
+      </c>
+      <c r="O629">
+        <v>1</v>
+      </c>
+      <c r="P629" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="630" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A630" t="s">
+        <v>665</v>
+      </c>
+      <c r="B630">
+        <v>2</v>
+      </c>
+      <c r="C630" t="s">
+        <v>17</v>
+      </c>
+      <c r="D630" t="s">
+        <v>34</v>
+      </c>
+      <c r="F630" t="s">
+        <v>17</v>
+      </c>
+      <c r="J630" t="s">
+        <v>17</v>
+      </c>
+      <c r="N630" t="s">
+        <v>17</v>
+      </c>
+      <c r="P630" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="631" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A631" t="s">
+        <v>666</v>
+      </c>
+      <c r="B631">
+        <v>2</v>
+      </c>
+      <c r="C631" t="s">
+        <v>20</v>
+      </c>
+      <c r="D631" t="s">
+        <v>44</v>
+      </c>
+      <c r="F631" t="s">
+        <v>17</v>
+      </c>
+      <c r="J631" t="s">
+        <v>17</v>
+      </c>
+      <c r="N631" t="s">
+        <v>17</v>
+      </c>
+      <c r="O631" t="s">
+        <v>48</v>
+      </c>
+      <c r="P631" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="632" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A632" t="s">
+        <v>667</v>
+      </c>
+      <c r="B632">
+        <v>2</v>
+      </c>
+      <c r="C632" t="s">
+        <v>17</v>
+      </c>
+      <c r="D632" t="s">
+        <v>34</v>
+      </c>
+      <c r="E632" t="s">
+        <v>30</v>
+      </c>
+      <c r="F632" t="s">
+        <v>20</v>
+      </c>
+      <c r="I632">
+        <v>7</v>
+      </c>
+      <c r="J632" t="s">
+        <v>17</v>
+      </c>
+      <c r="N632" t="s">
+        <v>20</v>
+      </c>
+      <c r="O632">
+        <v>1</v>
+      </c>
+      <c r="P632" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="633" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A633" t="s">
+        <v>668</v>
+      </c>
+      <c r="B633">
+        <v>2</v>
+      </c>
+      <c r="C633" t="s">
+        <v>17</v>
+      </c>
+      <c r="D633" t="s">
+        <v>34</v>
+      </c>
+      <c r="E633" t="s">
+        <v>28</v>
+      </c>
+      <c r="F633" t="s">
+        <v>17</v>
+      </c>
+      <c r="J633" t="s">
+        <v>17</v>
+      </c>
+      <c r="N633" t="s">
+        <v>17</v>
+      </c>
+      <c r="P633" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="634" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A634" t="s">
+        <v>669</v>
+      </c>
+      <c r="B634">
+        <v>3</v>
+      </c>
+      <c r="C634" t="s">
+        <v>17</v>
+      </c>
+      <c r="D634" t="s">
+        <v>27</v>
+      </c>
+      <c r="E634" t="s">
+        <v>19</v>
+      </c>
+      <c r="F634" t="s">
+        <v>20</v>
+      </c>
+      <c r="G634" t="s">
+        <v>21</v>
+      </c>
+      <c r="I634">
+        <v>19</v>
+      </c>
+      <c r="J634" t="s">
+        <v>17</v>
+      </c>
+      <c r="N634" t="s">
+        <v>20</v>
+      </c>
+      <c r="O634" t="s">
+        <v>52</v>
+      </c>
+      <c r="P634" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="635" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A635" t="s">
+        <v>670</v>
+      </c>
+      <c r="B635">
+        <v>2</v>
+      </c>
+      <c r="C635" t="s">
+        <v>17</v>
+      </c>
+      <c r="D635" t="s">
+        <v>44</v>
+      </c>
+      <c r="E635" t="s">
+        <v>30</v>
+      </c>
+      <c r="F635" t="s">
+        <v>17</v>
+      </c>
+      <c r="J635" t="s">
+        <v>17</v>
+      </c>
+      <c r="N635" t="s">
+        <v>20</v>
+      </c>
+      <c r="P635" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="636" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A636" t="s">
+        <v>671</v>
+      </c>
+      <c r="B636">
+        <v>6</v>
+      </c>
+      <c r="C636" t="s">
+        <v>17</v>
+      </c>
+      <c r="D636" t="s">
+        <v>44</v>
+      </c>
+      <c r="F636" t="s">
+        <v>20</v>
+      </c>
+      <c r="I636">
+        <v>7</v>
+      </c>
+      <c r="J636" t="s">
+        <v>20</v>
+      </c>
+      <c r="N636" t="s">
+        <v>20</v>
+      </c>
+      <c r="O636">
+        <v>1</v>
+      </c>
+      <c r="P636" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="637" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A637" t="s">
+        <v>672</v>
+      </c>
+      <c r="B637">
+        <v>5</v>
+      </c>
+      <c r="C637" t="s">
+        <v>17</v>
+      </c>
+      <c r="D637" t="s">
+        <v>44</v>
+      </c>
+      <c r="E637" t="s">
+        <v>25</v>
+      </c>
+      <c r="F637" t="s">
+        <v>20</v>
+      </c>
+      <c r="G637" t="s">
+        <v>79</v>
+      </c>
+      <c r="H637" t="s">
+        <v>42</v>
+      </c>
+      <c r="I637">
+        <v>14.5</v>
+      </c>
+      <c r="J637" t="s">
+        <v>17</v>
+      </c>
+      <c r="N637" t="s">
+        <v>17</v>
+      </c>
+      <c r="O637" t="s">
+        <v>48</v>
+      </c>
+      <c r="P637" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="638" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A638" t="s">
+        <v>673</v>
+      </c>
+      <c r="B638">
+        <v>6</v>
+      </c>
+      <c r="C638" t="s">
+        <v>20</v>
+      </c>
+      <c r="D638" t="s">
+        <v>32</v>
+      </c>
+      <c r="F638" t="s">
+        <v>20</v>
+      </c>
+      <c r="I638">
+        <v>17</v>
+      </c>
+      <c r="J638" t="s">
+        <v>17</v>
+      </c>
+      <c r="N638" t="s">
+        <v>17</v>
+      </c>
+      <c r="O638">
+        <v>3</v>
+      </c>
+      <c r="P638" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="639" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A639" t="s">
+        <v>674</v>
+      </c>
+      <c r="B639">
+        <v>5</v>
+      </c>
+      <c r="C639" t="s">
+        <v>20</v>
+      </c>
+      <c r="D639" t="s">
+        <v>55</v>
+      </c>
+      <c r="E639" t="s">
+        <v>25</v>
+      </c>
+      <c r="F639" t="s">
+        <v>20</v>
+      </c>
+      <c r="H639" t="s">
+        <v>42</v>
+      </c>
+      <c r="I639">
+        <v>10</v>
+      </c>
+      <c r="J639" t="s">
+        <v>17</v>
+      </c>
+      <c r="N639" t="s">
+        <v>17</v>
+      </c>
+      <c r="O639" t="s">
+        <v>48</v>
+      </c>
+      <c r="P639" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="640" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A640" t="s">
+        <v>675</v>
+      </c>
+      <c r="B640">
+        <v>2</v>
+      </c>
+      <c r="C640" t="s">
+        <v>20</v>
+      </c>
+      <c r="D640" t="s">
+        <v>18</v>
+      </c>
+      <c r="F640" t="s">
+        <v>17</v>
+      </c>
+      <c r="J640" t="s">
+        <v>17</v>
+      </c>
+      <c r="N640" t="s">
+        <v>20</v>
+      </c>
+      <c r="P640" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="641" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A641" t="s">
+        <v>676</v>
+      </c>
+      <c r="B641">
+        <v>5</v>
+      </c>
+      <c r="C641" t="s">
+        <v>17</v>
+      </c>
+      <c r="D641" t="s">
+        <v>44</v>
+      </c>
+      <c r="E641" t="s">
+        <v>28</v>
+      </c>
+      <c r="F641" t="s">
+        <v>20</v>
+      </c>
+      <c r="I641">
+        <v>12</v>
+      </c>
+      <c r="J641" t="s">
+        <v>20</v>
+      </c>
+      <c r="M641">
+        <v>7.4</v>
+      </c>
+      <c r="N641" t="s">
+        <v>17</v>
+      </c>
+      <c r="O641">
+        <v>3</v>
+      </c>
+      <c r="P641" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="642" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A642" t="s">
+        <v>677</v>
+      </c>
+      <c r="B642">
+        <v>4</v>
+      </c>
+      <c r="C642" t="s">
+        <v>17</v>
+      </c>
+      <c r="D642" t="s">
+        <v>34</v>
+      </c>
+      <c r="E642" t="s">
+        <v>25</v>
+      </c>
+      <c r="F642" t="s">
+        <v>17</v>
+      </c>
+      <c r="J642" t="s">
+        <v>20</v>
+      </c>
+      <c r="M642">
+        <v>10</v>
+      </c>
+      <c r="N642" t="s">
+        <v>20</v>
+      </c>
+      <c r="P642" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="643" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A643" t="s">
+        <v>678</v>
+      </c>
+      <c r="B643">
+        <v>1</v>
+      </c>
+      <c r="C643" t="s">
+        <v>17</v>
+      </c>
+      <c r="D643" t="s">
+        <v>34</v>
+      </c>
+      <c r="E643" t="s">
+        <v>28</v>
+      </c>
+      <c r="F643" t="s">
+        <v>17</v>
+      </c>
+      <c r="J643" t="s">
+        <v>17</v>
+      </c>
+      <c r="N643" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="644" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A644" t="s">
+        <v>679</v>
+      </c>
+      <c r="B644">
+        <v>4</v>
+      </c>
+      <c r="C644" t="s">
+        <v>17</v>
+      </c>
+      <c r="D644" t="s">
+        <v>34</v>
+      </c>
+      <c r="E644" t="s">
+        <v>30</v>
+      </c>
+      <c r="F644" t="s">
+        <v>20</v>
+      </c>
+      <c r="I644">
+        <v>10</v>
+      </c>
+      <c r="J644" t="s">
+        <v>17</v>
+      </c>
+      <c r="N644" t="s">
+        <v>20</v>
+      </c>
+      <c r="O644" t="s">
+        <v>52</v>
+      </c>
+      <c r="P644" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="645" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A645" t="s">
+        <v>680</v>
+      </c>
+      <c r="B645">
+        <v>2</v>
+      </c>
+      <c r="C645" t="s">
+        <v>20</v>
+      </c>
+      <c r="D645" t="s">
+        <v>18</v>
+      </c>
+      <c r="E645" t="s">
+        <v>30</v>
+      </c>
+      <c r="F645" t="s">
+        <v>20</v>
+      </c>
+      <c r="I645">
+        <v>14</v>
+      </c>
+      <c r="J645" t="s">
+        <v>17</v>
+      </c>
+      <c r="N645" t="s">
+        <v>20</v>
+      </c>
+      <c r="O645" t="s">
+        <v>52</v>
+      </c>
+      <c r="P645" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="646" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A646" t="s">
+        <v>681</v>
+      </c>
+      <c r="B646">
+        <v>2</v>
+      </c>
+      <c r="C646" t="s">
+        <v>17</v>
+      </c>
+      <c r="D646" t="s">
+        <v>34</v>
+      </c>
+      <c r="E646" t="s">
+        <v>28</v>
+      </c>
+      <c r="F646" t="s">
+        <v>20</v>
+      </c>
+      <c r="I646">
+        <v>25</v>
+      </c>
+      <c r="J646" t="s">
+        <v>17</v>
+      </c>
+      <c r="N646" t="s">
+        <v>20</v>
+      </c>
+      <c r="O646">
+        <v>1</v>
+      </c>
+      <c r="P646" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="647" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A647" t="s">
+        <v>682</v>
+      </c>
+      <c r="B647">
+        <v>2</v>
+      </c>
+      <c r="C647" t="s">
+        <v>17</v>
+      </c>
+      <c r="D647" t="s">
+        <v>34</v>
+      </c>
+      <c r="E647" t="s">
+        <v>30</v>
+      </c>
+      <c r="F647" t="s">
+        <v>20</v>
+      </c>
+      <c r="H647" t="s">
+        <v>34</v>
+      </c>
+      <c r="I647">
+        <v>8</v>
+      </c>
+      <c r="J647" t="s">
+        <v>17</v>
+      </c>
+      <c r="N647" t="s">
+        <v>17</v>
+      </c>
+      <c r="O647">
+        <v>1</v>
+      </c>
+      <c r="P647" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="648" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A648" t="s">
+        <v>683</v>
+      </c>
+      <c r="B648">
+        <v>4</v>
+      </c>
+      <c r="C648" t="s">
+        <v>17</v>
+      </c>
+      <c r="F648" t="s">
+        <v>17</v>
+      </c>
+      <c r="J648" t="s">
+        <v>20</v>
+      </c>
+      <c r="M648">
+        <v>40</v>
+      </c>
+      <c r="N648" t="s">
+        <v>20</v>
+      </c>
+      <c r="O648" t="s">
+        <v>48</v>
+      </c>
+      <c r="P648" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="649" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A649" t="s">
+        <v>684</v>
+      </c>
+      <c r="B649">
+        <v>1</v>
+      </c>
+      <c r="C649" t="s">
+        <v>20</v>
+      </c>
+      <c r="D649" t="s">
+        <v>18</v>
+      </c>
+      <c r="E649" t="s">
+        <v>25</v>
+      </c>
+      <c r="F649" t="s">
+        <v>17</v>
+      </c>
+      <c r="J649" t="s">
+        <v>17</v>
+      </c>
+      <c r="N649" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="650" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A650" t="s">
+        <v>685</v>
+      </c>
+      <c r="B650">
+        <v>2</v>
+      </c>
+      <c r="C650" t="s">
+        <v>20</v>
+      </c>
+      <c r="D650" t="s">
+        <v>27</v>
+      </c>
+      <c r="E650" t="s">
+        <v>30</v>
+      </c>
+      <c r="F650" t="s">
+        <v>20</v>
+      </c>
+      <c r="H650" t="s">
+        <v>34</v>
+      </c>
+      <c r="I650">
+        <v>7.5</v>
+      </c>
+      <c r="J650" t="s">
+        <v>17</v>
+      </c>
+      <c r="N650" t="s">
+        <v>17</v>
+      </c>
+      <c r="O650">
+        <v>1</v>
+      </c>
+      <c r="P650" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="651" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A651" t="s">
+        <v>686</v>
+      </c>
+      <c r="B651">
+        <v>2</v>
+      </c>
+      <c r="C651" t="s">
+        <v>20</v>
+      </c>
+      <c r="D651" t="s">
+        <v>44</v>
+      </c>
+      <c r="E651" t="s">
+        <v>25</v>
+      </c>
+      <c r="F651" t="s">
+        <v>20</v>
+      </c>
+      <c r="G651" t="s">
+        <v>21</v>
+      </c>
+      <c r="I651">
+        <v>6.2</v>
+      </c>
+      <c r="J651" t="s">
+        <v>17</v>
+      </c>
+      <c r="N651" t="s">
+        <v>17</v>
+      </c>
+      <c r="O651">
+        <v>1</v>
+      </c>
+      <c r="P651" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="652" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A652" t="s">
+        <v>687</v>
+      </c>
+      <c r="B652">
+        <v>2</v>
+      </c>
+      <c r="C652" t="s">
+        <v>17</v>
+      </c>
+      <c r="D652" t="s">
+        <v>34</v>
+      </c>
+      <c r="E652" t="s">
+        <v>25</v>
+      </c>
+      <c r="F652" t="s">
+        <v>20</v>
+      </c>
+      <c r="H652" t="s">
+        <v>34</v>
+      </c>
+      <c r="I652">
+        <v>21</v>
+      </c>
+      <c r="J652" t="s">
+        <v>17</v>
+      </c>
+      <c r="N652" t="s">
+        <v>17</v>
+      </c>
+      <c r="P652" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="653" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A653" t="s">
+        <v>688</v>
+      </c>
+      <c r="B653">
+        <v>5</v>
+      </c>
+      <c r="C653" t="s">
+        <v>17</v>
+      </c>
+      <c r="D653" t="s">
+        <v>34</v>
+      </c>
+      <c r="E653" t="s">
+        <v>25</v>
+      </c>
+      <c r="F653" t="s">
+        <v>20</v>
+      </c>
+      <c r="H653" t="s">
+        <v>42</v>
+      </c>
+      <c r="I653">
+        <v>10</v>
+      </c>
+      <c r="J653" t="s">
+        <v>17</v>
+      </c>
+      <c r="N653" t="s">
+        <v>20</v>
+      </c>
+      <c r="O653">
+        <v>3</v>
+      </c>
+      <c r="P653" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="654" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A654" t="s">
+        <v>689</v>
+      </c>
+      <c r="B654">
+        <v>4</v>
+      </c>
+      <c r="C654" t="s">
+        <v>17</v>
+      </c>
+      <c r="D654" t="s">
+        <v>32</v>
+      </c>
+      <c r="E654" t="s">
+        <v>28</v>
+      </c>
+      <c r="F654" t="s">
+        <v>20</v>
+      </c>
+      <c r="I654">
+        <v>5.5</v>
+      </c>
+      <c r="J654" t="s">
+        <v>20</v>
+      </c>
+      <c r="M654">
+        <v>109</v>
+      </c>
+      <c r="N654" t="s">
+        <v>20</v>
+      </c>
+      <c r="O654">
+        <v>2</v>
+      </c>
+      <c r="P654" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="655" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A655" t="s">
+        <v>690</v>
+      </c>
+      <c r="B655">
+        <v>5</v>
+      </c>
+      <c r="C655" t="s">
+        <v>20</v>
+      </c>
+      <c r="D655" t="s">
+        <v>34</v>
+      </c>
+      <c r="F655" t="s">
+        <v>20</v>
+      </c>
+      <c r="I655">
+        <v>36</v>
+      </c>
+      <c r="J655" t="s">
+        <v>17</v>
+      </c>
+      <c r="N655" t="s">
+        <v>20</v>
+      </c>
+      <c r="O655">
+        <v>3</v>
+      </c>
+      <c r="P655" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="656" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A656" t="s">
+        <v>691</v>
+      </c>
+      <c r="B656">
+        <v>6</v>
+      </c>
+      <c r="C656" t="s">
+        <v>17</v>
+      </c>
+      <c r="D656" t="s">
+        <v>55</v>
+      </c>
+      <c r="E656" t="s">
+        <v>25</v>
+      </c>
+      <c r="F656" t="s">
+        <v>17</v>
+      </c>
+      <c r="J656" t="s">
+        <v>20</v>
+      </c>
+      <c r="M656">
+        <v>20</v>
+      </c>
+      <c r="N656" t="s">
+        <v>17</v>
+      </c>
+      <c r="O656">
+        <v>2</v>
+      </c>
+      <c r="P656" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="657" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A657" t="s">
+        <v>692</v>
+      </c>
+      <c r="B657">
+        <v>6</v>
+      </c>
+      <c r="C657" t="s">
+        <v>17</v>
+      </c>
+      <c r="D657" t="s">
+        <v>44</v>
+      </c>
+      <c r="F657" t="s">
+        <v>17</v>
+      </c>
+      <c r="J657" t="s">
+        <v>17</v>
+      </c>
+      <c r="N657" t="s">
+        <v>17</v>
+      </c>
+      <c r="P657" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="658" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A658" t="s">
+        <v>693</v>
+      </c>
+      <c r="B658">
+        <v>6</v>
+      </c>
+      <c r="C658" t="s">
+        <v>17</v>
+      </c>
+      <c r="D658" t="s">
+        <v>32</v>
+      </c>
+      <c r="F658" t="s">
+        <v>20</v>
+      </c>
+      <c r="H658" t="s">
+        <v>34</v>
+      </c>
+      <c r="I658">
+        <v>15</v>
+      </c>
+      <c r="J658" t="s">
+        <v>20</v>
+      </c>
+      <c r="M658">
+        <v>5</v>
+      </c>
+      <c r="N658" t="s">
+        <v>17</v>
+      </c>
+      <c r="O658">
+        <v>3</v>
+      </c>
+      <c r="P658" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="659" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A659" t="s">
+        <v>694</v>
+      </c>
+      <c r="B659">
+        <v>4</v>
+      </c>
+      <c r="C659" t="s">
+        <v>17</v>
+      </c>
+      <c r="D659" t="s">
+        <v>34</v>
+      </c>
+      <c r="E659" t="s">
+        <v>19</v>
+      </c>
+      <c r="F659" t="s">
+        <v>20</v>
+      </c>
+      <c r="I659">
+        <v>5</v>
+      </c>
+      <c r="J659" t="s">
+        <v>20</v>
+      </c>
+      <c r="M659">
+        <v>6</v>
+      </c>
+      <c r="N659" t="s">
+        <v>20</v>
+      </c>
+      <c r="O659" t="s">
+        <v>52</v>
+      </c>
+      <c r="P659" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="660" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A660" t="s">
+        <v>695</v>
+      </c>
+      <c r="B660">
+        <v>6</v>
+      </c>
+      <c r="C660" t="s">
+        <v>17</v>
+      </c>
+      <c r="D660" t="s">
+        <v>18</v>
+      </c>
+      <c r="E660" t="s">
+        <v>19</v>
+      </c>
+      <c r="F660" t="s">
+        <v>20</v>
+      </c>
+      <c r="H660" t="s">
+        <v>42</v>
+      </c>
+      <c r="I660">
+        <v>55</v>
+      </c>
+      <c r="J660" t="s">
+        <v>17</v>
+      </c>
+      <c r="N660" t="s">
+        <v>17</v>
+      </c>
+      <c r="O660" t="s">
+        <v>48</v>
+      </c>
+      <c r="P660" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="661" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A661" t="s">
+        <v>696</v>
+      </c>
+      <c r="B661">
+        <v>6</v>
+      </c>
+      <c r="C661" t="s">
+        <v>17</v>
+      </c>
+      <c r="D661" t="s">
+        <v>34</v>
+      </c>
+      <c r="E661" t="s">
+        <v>25</v>
+      </c>
+      <c r="F661" t="s">
+        <v>20</v>
+      </c>
+      <c r="J661" t="s">
+        <v>17</v>
+      </c>
+      <c r="N661" t="s">
+        <v>17</v>
+      </c>
+      <c r="P661" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="662" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A662" t="s">
+        <v>697</v>
+      </c>
+      <c r="B662">
+        <v>6</v>
+      </c>
+      <c r="C662" t="s">
+        <v>17</v>
+      </c>
+      <c r="D662" t="s">
+        <v>34</v>
+      </c>
+      <c r="F662" t="s">
+        <v>20</v>
+      </c>
+      <c r="I662">
+        <v>8</v>
+      </c>
+      <c r="J662" t="s">
+        <v>20</v>
+      </c>
+      <c r="N662" t="s">
+        <v>20</v>
+      </c>
+      <c r="O662" t="s">
+        <v>52</v>
+      </c>
+      <c r="P662" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="663" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A663" t="s">
+        <v>698</v>
+      </c>
+      <c r="B663">
+        <v>2</v>
+      </c>
+      <c r="C663" t="s">
+        <v>17</v>
+      </c>
+      <c r="D663" t="s">
+        <v>32</v>
+      </c>
+      <c r="E663" t="s">
+        <v>28</v>
+      </c>
+      <c r="F663" t="s">
+        <v>17</v>
+      </c>
+      <c r="J663" t="s">
+        <v>17</v>
+      </c>
+      <c r="N663" t="s">
+        <v>17</v>
+      </c>
+      <c r="O663">
+        <v>1</v>
+      </c>
+      <c r="P663" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="664" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A664" t="s">
+        <v>699</v>
+      </c>
+      <c r="B664">
+        <v>2</v>
+      </c>
+      <c r="C664" t="s">
+        <v>17</v>
+      </c>
+      <c r="D664" t="s">
+        <v>34</v>
+      </c>
+      <c r="E664" t="s">
+        <v>25</v>
+      </c>
+      <c r="F664" t="s">
+        <v>20</v>
+      </c>
+      <c r="J664" t="s">
+        <v>17</v>
+      </c>
+      <c r="N664" t="s">
+        <v>17</v>
+      </c>
+      <c r="P664" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="665" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A665" t="s">
+        <v>700</v>
+      </c>
+      <c r="B665">
+        <v>2</v>
+      </c>
+      <c r="C665" t="s">
+        <v>17</v>
+      </c>
+      <c r="D665" t="s">
+        <v>44</v>
+      </c>
+      <c r="E665" t="s">
+        <v>28</v>
+      </c>
+      <c r="F665" t="s">
+        <v>17</v>
+      </c>
+      <c r="J665" t="s">
+        <v>17</v>
+      </c>
+      <c r="N665" t="s">
+        <v>20</v>
+      </c>
+      <c r="O665">
+        <v>1</v>
+      </c>
+      <c r="P665" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="666" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A666" t="s">
+        <v>701</v>
+      </c>
+      <c r="B666">
+        <v>1</v>
+      </c>
+      <c r="C666" t="s">
+        <v>17</v>
+      </c>
+      <c r="D666" t="s">
+        <v>55</v>
+      </c>
+      <c r="E666" t="s">
+        <v>25</v>
+      </c>
+      <c r="F666" t="s">
+        <v>17</v>
+      </c>
+      <c r="J666" t="s">
+        <v>17</v>
+      </c>
+      <c r="N666" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="667" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A667" t="s">
+        <v>702</v>
+      </c>
+      <c r="B667">
+        <v>4</v>
+      </c>
+      <c r="C667" t="s">
+        <v>20</v>
+      </c>
+      <c r="D667" t="s">
+        <v>34</v>
+      </c>
+      <c r="E667" t="s">
+        <v>25</v>
+      </c>
+      <c r="F667" t="s">
+        <v>20</v>
+      </c>
+      <c r="I667">
+        <v>6</v>
+      </c>
+      <c r="J667" t="s">
+        <v>17</v>
+      </c>
+      <c r="N667" t="s">
+        <v>20</v>
+      </c>
+      <c r="O667">
+        <v>3</v>
+      </c>
+      <c r="P667" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="668" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A668" t="s">
+        <v>703</v>
+      </c>
+      <c r="B668">
+        <v>5</v>
+      </c>
+      <c r="C668" t="s">
+        <v>17</v>
+      </c>
+      <c r="D668" t="s">
+        <v>44</v>
+      </c>
+      <c r="E668" t="s">
+        <v>28</v>
+      </c>
+      <c r="F668" t="s">
+        <v>20</v>
+      </c>
+      <c r="I668">
+        <v>19</v>
+      </c>
+      <c r="J668" t="s">
+        <v>17</v>
+      </c>
+      <c r="N668" t="s">
+        <v>17</v>
+      </c>
+      <c r="O668">
+        <v>3</v>
+      </c>
+      <c r="P668" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="669" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A669" t="s">
+        <v>704</v>
+      </c>
+      <c r="B669">
+        <v>2</v>
+      </c>
+      <c r="C669" t="s">
+        <v>20</v>
+      </c>
+      <c r="D669" t="s">
+        <v>36</v>
+      </c>
+      <c r="F669" t="s">
+        <v>17</v>
+      </c>
+      <c r="J669" t="s">
+        <v>17</v>
+      </c>
+      <c r="N669" t="s">
+        <v>17</v>
+      </c>
+      <c r="P669" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="670" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A670" t="s">
+        <v>705</v>
+      </c>
+      <c r="B670">
+        <v>2</v>
+      </c>
+      <c r="C670" t="s">
+        <v>17</v>
+      </c>
+      <c r="D670" t="s">
+        <v>34</v>
+      </c>
+      <c r="E670" t="s">
+        <v>25</v>
+      </c>
+      <c r="F670" t="s">
+        <v>20</v>
+      </c>
+      <c r="J670" t="s">
+        <v>20</v>
+      </c>
+      <c r="M670">
+        <v>3</v>
+      </c>
+      <c r="N670" t="s">
+        <v>20</v>
+      </c>
+      <c r="P670" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="671" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A671" t="s">
+        <v>706</v>
+      </c>
+      <c r="B671">
+        <v>5</v>
+      </c>
+      <c r="C671" t="s">
+        <v>17</v>
+      </c>
+      <c r="F671" t="s">
+        <v>20</v>
+      </c>
+      <c r="H671" t="s">
+        <v>42</v>
+      </c>
+      <c r="I671">
+        <v>40</v>
+      </c>
+      <c r="J671" t="s">
+        <v>17</v>
+      </c>
+      <c r="N671" t="s">
+        <v>17</v>
+      </c>
+      <c r="O671">
+        <v>3</v>
+      </c>
+      <c r="P671" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="672" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A672" t="s">
+        <v>707</v>
+      </c>
+      <c r="B672">
+        <v>0</v>
+      </c>
+      <c r="C672" t="s">
+        <v>17</v>
+      </c>
+      <c r="D672" t="s">
+        <v>44</v>
+      </c>
+      <c r="E672" t="s">
+        <v>25</v>
+      </c>
+      <c r="F672" t="s">
+        <v>20</v>
+      </c>
+      <c r="I672">
+        <v>9</v>
+      </c>
+      <c r="J672" t="s">
+        <v>17</v>
+      </c>
+      <c r="N672" t="s">
+        <v>20</v>
+      </c>
+      <c r="P672" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="673" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A673" t="s">
+        <v>708</v>
+      </c>
+      <c r="C673" t="s">
+        <v>20</v>
+      </c>
+      <c r="F673" t="s">
+        <v>20</v>
+      </c>
+      <c r="I673">
+        <v>27</v>
+      </c>
+      <c r="J673" t="s">
+        <v>17</v>
+      </c>
+      <c r="N673" t="s">
+        <v>17</v>
+      </c>
+      <c r="P673" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="674" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A674" t="s">
+        <v>709</v>
+      </c>
+      <c r="B674">
+        <v>5</v>
+      </c>
+      <c r="C674" t="s">
+        <v>17</v>
+      </c>
+      <c r="D674" t="s">
+        <v>36</v>
+      </c>
+      <c r="E674" t="s">
+        <v>25</v>
+      </c>
+      <c r="F674" t="s">
+        <v>20</v>
+      </c>
+      <c r="I674">
+        <v>9</v>
+      </c>
+      <c r="J674" t="s">
+        <v>20</v>
+      </c>
+      <c r="N674" t="s">
+        <v>17</v>
+      </c>
+      <c r="O674">
+        <v>3</v>
+      </c>
+      <c r="P674" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="675" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A675" t="s">
+        <v>710</v>
+      </c>
+      <c r="B675">
+        <v>2</v>
+      </c>
+      <c r="C675" t="s">
+        <v>17</v>
+      </c>
+      <c r="D675" t="s">
+        <v>34</v>
+      </c>
+      <c r="E675" t="s">
+        <v>25</v>
+      </c>
+      <c r="F675" t="s">
+        <v>20</v>
+      </c>
+      <c r="I675">
+        <v>6</v>
+      </c>
+      <c r="J675" t="s">
+        <v>17</v>
+      </c>
+      <c r="N675" t="s">
+        <v>17</v>
+      </c>
+      <c r="O675">
+        <v>1</v>
+      </c>
+      <c r="P675" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="676" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A676" t="s">
+        <v>711</v>
+      </c>
+      <c r="B676">
+        <v>2</v>
+      </c>
+      <c r="C676" t="s">
+        <v>17</v>
+      </c>
+      <c r="D676" t="s">
+        <v>34</v>
+      </c>
+      <c r="E676" t="s">
+        <v>25</v>
+      </c>
+      <c r="F676" t="s">
+        <v>17</v>
+      </c>
+      <c r="J676" t="s">
+        <v>17</v>
+      </c>
+      <c r="N676" t="s">
+        <v>20</v>
+      </c>
+      <c r="P676" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="677" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A677" t="s">
+        <v>712</v>
+      </c>
+      <c r="B677">
+        <v>2</v>
+      </c>
+      <c r="C677" t="s">
+        <v>20</v>
+      </c>
+      <c r="D677" t="s">
+        <v>18</v>
+      </c>
+      <c r="E677" t="s">
+        <v>19</v>
+      </c>
+      <c r="F677" t="s">
+        <v>17</v>
+      </c>
+      <c r="J677" t="s">
+        <v>17</v>
+      </c>
+      <c r="N677" t="s">
+        <v>20</v>
+      </c>
+      <c r="P677" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="678" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A678" t="s">
+        <v>713</v>
+      </c>
+      <c r="B678">
+        <v>2</v>
+      </c>
+      <c r="C678" t="s">
+        <v>17</v>
+      </c>
+      <c r="D678" t="s">
+        <v>55</v>
+      </c>
+      <c r="E678" t="s">
+        <v>25</v>
+      </c>
+      <c r="F678" t="s">
+        <v>17</v>
+      </c>
+      <c r="J678" t="s">
+        <v>17</v>
+      </c>
+      <c r="N678" t="s">
+        <v>20</v>
+      </c>
+      <c r="P678" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="679" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A679" t="s">
+        <v>714</v>
+      </c>
+      <c r="B679">
+        <v>2</v>
+      </c>
+      <c r="C679" t="s">
+        <v>17</v>
+      </c>
+      <c r="D679" t="s">
+        <v>44</v>
+      </c>
+      <c r="E679" t="s">
+        <v>25</v>
+      </c>
+      <c r="F679" t="s">
+        <v>17</v>
+      </c>
+      <c r="J679" t="s">
+        <v>17</v>
+      </c>
+      <c r="N679" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="680" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A680" t="s">
+        <v>715</v>
+      </c>
+      <c r="B680">
+        <v>2</v>
+      </c>
+      <c r="C680" t="s">
+        <v>20</v>
+      </c>
+      <c r="D680" t="s">
+        <v>34</v>
+      </c>
+      <c r="E680" t="s">
+        <v>25</v>
+      </c>
+      <c r="F680" t="s">
+        <v>17</v>
+      </c>
+      <c r="J680" t="s">
+        <v>17</v>
+      </c>
+      <c r="N680" t="s">
+        <v>20</v>
+      </c>
+      <c r="P680" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="681" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A681" t="s">
+        <v>716</v>
+      </c>
+      <c r="B681">
+        <v>4</v>
+      </c>
+      <c r="C681" t="s">
+        <v>20</v>
+      </c>
+      <c r="D681" t="s">
+        <v>44</v>
+      </c>
+      <c r="E681" t="s">
+        <v>25</v>
+      </c>
+      <c r="F681" t="s">
+        <v>17</v>
+      </c>
+      <c r="J681" t="s">
+        <v>20</v>
+      </c>
+      <c r="M681">
+        <v>13</v>
+      </c>
+      <c r="N681" t="s">
+        <v>20</v>
+      </c>
+      <c r="O681">
+        <v>1</v>
+      </c>
+      <c r="P681" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="682" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A682" t="s">
+        <v>717</v>
+      </c>
+      <c r="B682">
+        <v>2</v>
+      </c>
+      <c r="C682" t="s">
+        <v>17</v>
+      </c>
+      <c r="D682" t="s">
+        <v>18</v>
+      </c>
+      <c r="E682" t="s">
+        <v>30</v>
+      </c>
+      <c r="F682" t="s">
+        <v>17</v>
+      </c>
+      <c r="J682" t="s">
+        <v>17</v>
+      </c>
+      <c r="N682" t="s">
+        <v>20</v>
+      </c>
+      <c r="P682" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="683" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A683" t="s">
+        <v>718</v>
+      </c>
+      <c r="B683">
+        <v>2</v>
+      </c>
+      <c r="C683" t="s">
+        <v>20</v>
+      </c>
+      <c r="D683" t="s">
+        <v>34</v>
+      </c>
+      <c r="E683" t="s">
+        <v>30</v>
+      </c>
+      <c r="F683" t="s">
+        <v>20</v>
+      </c>
+      <c r="J683" t="s">
+        <v>17</v>
+      </c>
+      <c r="N683" t="s">
+        <v>20</v>
+      </c>
+      <c r="P683" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="684" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A684" t="s">
+        <v>719</v>
+      </c>
+      <c r="B684">
+        <v>4</v>
+      </c>
+      <c r="C684" t="s">
+        <v>17</v>
+      </c>
+      <c r="D684" t="s">
+        <v>34</v>
+      </c>
+      <c r="E684" t="s">
+        <v>25</v>
+      </c>
+      <c r="F684" t="s">
+        <v>20</v>
+      </c>
+      <c r="I684">
+        <v>13</v>
+      </c>
+      <c r="J684" t="s">
+        <v>17</v>
+      </c>
+      <c r="N684" t="s">
+        <v>17</v>
+      </c>
+      <c r="O684" t="s">
+        <v>52</v>
+      </c>
+      <c r="P684" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="685" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A685" t="s">
+        <v>720</v>
+      </c>
+      <c r="B685">
+        <v>2</v>
+      </c>
+      <c r="C685" t="s">
+        <v>17</v>
+      </c>
+      <c r="D685" t="s">
+        <v>34</v>
+      </c>
+      <c r="E685" t="s">
+        <v>25</v>
+      </c>
+      <c r="F685" t="s">
+        <v>17</v>
+      </c>
+      <c r="J685" t="s">
+        <v>17</v>
+      </c>
+      <c r="N685" t="s">
+        <v>20</v>
+      </c>
+      <c r="P685" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="686" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A686" t="s">
+        <v>721</v>
+      </c>
+      <c r="B686">
+        <v>1</v>
+      </c>
+      <c r="C686" t="s">
+        <v>17</v>
+      </c>
+      <c r="D686" t="s">
+        <v>32</v>
+      </c>
+      <c r="E686" t="s">
+        <v>28</v>
+      </c>
+      <c r="F686" t="s">
+        <v>17</v>
+      </c>
+      <c r="J686" t="s">
+        <v>17</v>
+      </c>
+      <c r="N686" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="687" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A687" t="s">
+        <v>722</v>
+      </c>
+      <c r="B687">
+        <v>2</v>
+      </c>
+      <c r="C687" t="s">
+        <v>17</v>
+      </c>
+      <c r="D687" t="s">
+        <v>34</v>
+      </c>
+      <c r="E687" t="s">
+        <v>25</v>
+      </c>
+      <c r="F687" t="s">
+        <v>20</v>
+      </c>
+      <c r="I687">
+        <v>6</v>
+      </c>
+      <c r="J687" t="s">
+        <v>17</v>
+      </c>
+      <c r="N687" t="s">
+        <v>17</v>
+      </c>
+      <c r="O687">
+        <v>2</v>
+      </c>
+      <c r="P687" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="688" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A688" t="s">
+        <v>723</v>
+      </c>
+      <c r="B688">
+        <v>3</v>
+      </c>
+      <c r="C688" t="s">
+        <v>17</v>
+      </c>
+      <c r="D688" t="s">
+        <v>32</v>
+      </c>
+      <c r="E688" t="s">
+        <v>28</v>
+      </c>
+      <c r="F688" t="s">
+        <v>20</v>
+      </c>
+      <c r="I688">
+        <v>3</v>
+      </c>
+      <c r="J688" t="s">
+        <v>17</v>
+      </c>
+      <c r="N688" t="s">
+        <v>20</v>
+      </c>
+      <c r="O688">
+        <v>3</v>
+      </c>
+      <c r="P688" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="689" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A689" t="s">
+        <v>724</v>
+      </c>
+      <c r="B689">
+        <v>2</v>
+      </c>
+      <c r="C689" t="s">
+        <v>20</v>
+      </c>
+      <c r="D689" t="s">
+        <v>32</v>
+      </c>
+      <c r="E689" t="s">
+        <v>28</v>
+      </c>
+      <c r="F689" t="s">
+        <v>20</v>
+      </c>
+      <c r="J689" t="s">
+        <v>17</v>
+      </c>
+      <c r="N689" t="s">
+        <v>17</v>
+      </c>
+      <c r="P689" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="690" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A690" t="s">
+        <v>725</v>
+      </c>
+      <c r="B690">
+        <v>2</v>
+      </c>
+      <c r="C690" t="s">
+        <v>17</v>
+      </c>
+      <c r="D690" t="s">
+        <v>18</v>
+      </c>
+      <c r="E690" t="s">
+        <v>30</v>
+      </c>
+      <c r="F690" t="s">
+        <v>20</v>
+      </c>
+      <c r="I690">
+        <v>14</v>
+      </c>
+      <c r="J690" t="s">
+        <v>20</v>
+      </c>
+      <c r="N690" t="s">
+        <v>17</v>
+      </c>
+      <c r="O690">
+        <v>1</v>
+      </c>
+      <c r="P690" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="691" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A691" t="s">
+        <v>726</v>
+      </c>
+      <c r="B691">
+        <v>4</v>
+      </c>
+      <c r="C691" t="s">
+        <v>20</v>
+      </c>
+      <c r="D691" t="s">
+        <v>44</v>
+      </c>
+      <c r="E691" t="s">
+        <v>30</v>
+      </c>
+      <c r="F691" t="s">
+        <v>20</v>
+      </c>
+      <c r="I691">
+        <v>4</v>
+      </c>
+      <c r="J691" t="s">
+        <v>17</v>
+      </c>
+      <c r="N691" t="s">
+        <v>17</v>
+      </c>
+      <c r="P691" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="692" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A692" t="s">
+        <v>727</v>
+      </c>
+      <c r="B692">
+        <v>4</v>
+      </c>
+      <c r="C692" t="s">
+        <v>20</v>
+      </c>
+      <c r="D692" t="s">
+        <v>34</v>
+      </c>
+      <c r="E692" t="s">
+        <v>30</v>
+      </c>
+      <c r="F692" t="s">
+        <v>17</v>
+      </c>
+      <c r="J692" t="s">
+        <v>20</v>
+      </c>
+      <c r="M692">
+        <v>71</v>
+      </c>
+      <c r="N692" t="s">
+        <v>17</v>
+      </c>
+      <c r="O692">
+        <v>3</v>
+      </c>
+      <c r="P692" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="693" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A693" t="s">
+        <v>728</v>
+      </c>
+      <c r="B693">
+        <v>2</v>
+      </c>
+      <c r="C693" t="s">
+        <v>17</v>
+      </c>
+      <c r="D693" t="s">
+        <v>55</v>
+      </c>
+      <c r="E693" t="s">
+        <v>25</v>
+      </c>
+      <c r="F693" t="s">
+        <v>20</v>
+      </c>
+      <c r="I693">
+        <v>7</v>
+      </c>
+      <c r="J693" t="s">
+        <v>17</v>
+      </c>
+      <c r="N693" t="s">
+        <v>17</v>
+      </c>
+      <c r="O693">
+        <v>3</v>
+      </c>
+      <c r="P693" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="694" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A694" t="s">
+        <v>729</v>
+      </c>
+      <c r="B694">
+        <v>2</v>
+      </c>
+      <c r="C694" t="s">
+        <v>17</v>
+      </c>
+      <c r="D694" t="s">
+        <v>44</v>
+      </c>
+      <c r="E694" t="s">
+        <v>25</v>
+      </c>
+      <c r="F694" t="s">
+        <v>20</v>
+      </c>
+      <c r="I694">
+        <v>13</v>
+      </c>
+      <c r="J694" t="s">
+        <v>17</v>
+      </c>
+      <c r="N694" t="s">
+        <v>20</v>
+      </c>
+      <c r="P694" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="695" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A695" t="s">
+        <v>730</v>
+      </c>
+      <c r="B695">
+        <v>5</v>
+      </c>
+      <c r="C695" t="s">
+        <v>17</v>
+      </c>
+      <c r="D695" t="s">
+        <v>34</v>
+      </c>
+      <c r="E695" t="s">
+        <v>25</v>
+      </c>
+      <c r="F695" t="s">
+        <v>20</v>
+      </c>
+      <c r="I695">
+        <v>33</v>
+      </c>
+      <c r="J695" t="s">
+        <v>20</v>
+      </c>
+      <c r="M695">
+        <v>15</v>
+      </c>
+      <c r="N695" t="s">
+        <v>17</v>
+      </c>
+      <c r="O695">
+        <v>3</v>
+      </c>
+      <c r="P695" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="696" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A696" t="s">
+        <v>731</v>
+      </c>
+      <c r="B696">
+        <v>0</v>
+      </c>
+      <c r="C696" t="s">
+        <v>17</v>
+      </c>
+      <c r="D696" t="s">
+        <v>44</v>
+      </c>
+      <c r="E696" t="s">
+        <v>30</v>
+      </c>
+      <c r="F696" t="s">
+        <v>20</v>
+      </c>
+      <c r="I696">
+        <v>4</v>
+      </c>
+      <c r="J696" t="s">
+        <v>17</v>
+      </c>
+      <c r="N696" t="s">
+        <v>20</v>
+      </c>
+      <c r="O696" t="s">
+        <v>48</v>
+      </c>
+      <c r="P696" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="697" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A697" t="s">
+        <v>732</v>
+      </c>
+      <c r="B697">
+        <v>1</v>
+      </c>
+      <c r="C697" t="s">
+        <v>17</v>
+      </c>
+      <c r="D697" t="s">
+        <v>44</v>
+      </c>
+      <c r="E697" t="s">
+        <v>25</v>
+      </c>
+      <c r="F697" t="s">
+        <v>17</v>
+      </c>
+      <c r="J697" t="s">
+        <v>17</v>
+      </c>
+      <c r="N697" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="698" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A698" t="s">
+        <v>733</v>
+      </c>
+      <c r="B698">
+        <v>2</v>
+      </c>
+      <c r="C698" t="s">
+        <v>20</v>
+      </c>
+      <c r="D698" t="s">
+        <v>34</v>
+      </c>
+      <c r="E698" t="s">
+        <v>25</v>
+      </c>
+      <c r="F698" t="s">
+        <v>17</v>
+      </c>
+      <c r="J698" t="s">
+        <v>17</v>
+      </c>
+      <c r="N698" t="s">
+        <v>20</v>
+      </c>
+      <c r="P698" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="699" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A699" t="s">
+        <v>734</v>
+      </c>
+      <c r="B699">
+        <v>2</v>
+      </c>
+      <c r="C699" t="s">
+        <v>17</v>
+      </c>
+      <c r="D699" t="s">
+        <v>18</v>
+      </c>
+      <c r="E699" t="s">
+        <v>30</v>
+      </c>
+      <c r="F699" t="s">
+        <v>20</v>
+      </c>
+      <c r="H699" t="s">
+        <v>42</v>
+      </c>
+      <c r="I699">
+        <v>25</v>
+      </c>
+      <c r="J699" t="s">
+        <v>17</v>
+      </c>
+      <c r="N699" t="s">
+        <v>20</v>
+      </c>
+      <c r="O699">
+        <v>1</v>
+      </c>
+      <c r="P699" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="700" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A700" t="s">
+        <v>735</v>
+      </c>
+      <c r="B700">
+        <v>2</v>
+      </c>
+      <c r="C700" t="s">
+        <v>17</v>
+      </c>
+      <c r="D700" t="s">
+        <v>18</v>
+      </c>
+      <c r="E700" t="s">
+        <v>19</v>
+      </c>
+      <c r="F700" t="s">
+        <v>17</v>
+      </c>
+      <c r="J700" t="s">
+        <v>17</v>
+      </c>
+      <c r="N700" t="s">
+        <v>20</v>
+      </c>
+      <c r="P700" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="701" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A701" t="s">
+        <v>736</v>
+      </c>
+      <c r="B701">
+        <v>4</v>
+      </c>
+      <c r="C701" t="s">
+        <v>20</v>
+      </c>
+      <c r="D701" t="s">
+        <v>34</v>
+      </c>
+      <c r="E701" t="s">
+        <v>25</v>
+      </c>
+      <c r="F701" t="s">
+        <v>20</v>
+      </c>
+      <c r="I701">
+        <v>6</v>
+      </c>
+      <c r="J701" t="s">
+        <v>17</v>
+      </c>
+      <c r="N701" t="s">
+        <v>17</v>
+      </c>
+      <c r="O701" t="s">
+        <v>52</v>
+      </c>
+      <c r="P701" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="702" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A702" t="s">
+        <v>737</v>
+      </c>
+      <c r="B702">
+        <v>2</v>
+      </c>
+      <c r="C702" t="s">
+        <v>17</v>
+      </c>
+      <c r="D702" t="s">
+        <v>32</v>
+      </c>
+      <c r="E702" t="s">
+        <v>25</v>
+      </c>
+      <c r="F702" t="s">
+        <v>20</v>
+      </c>
+      <c r="J702" t="s">
+        <v>17</v>
+      </c>
+      <c r="N702" t="s">
+        <v>20</v>
+      </c>
+      <c r="P702" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="703" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A703" t="s">
+        <v>738</v>
+      </c>
+      <c r="B703">
+        <v>4</v>
+      </c>
+      <c r="C703" t="s">
+        <v>17</v>
+      </c>
+      <c r="D703" t="s">
+        <v>18</v>
+      </c>
+      <c r="E703" t="s">
+        <v>30</v>
+      </c>
+      <c r="F703" t="s">
+        <v>17</v>
+      </c>
+      <c r="J703" t="s">
+        <v>20</v>
+      </c>
+      <c r="M703">
+        <v>12</v>
+      </c>
+      <c r="N703" t="s">
+        <v>17</v>
+      </c>
+      <c r="P703" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="704" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A704" t="s">
+        <v>739</v>
+      </c>
+      <c r="B704">
+        <v>6</v>
+      </c>
+      <c r="C704" t="s">
+        <v>17</v>
+      </c>
+      <c r="D704" t="s">
+        <v>44</v>
+      </c>
+      <c r="E704" t="s">
+        <v>25</v>
+      </c>
+      <c r="F704" t="s">
+        <v>20</v>
+      </c>
+      <c r="H704" t="s">
+        <v>42</v>
+      </c>
+      <c r="I704">
+        <v>33</v>
+      </c>
+      <c r="J704" t="s">
+        <v>20</v>
+      </c>
+      <c r="N704" t="s">
+        <v>17</v>
+      </c>
+      <c r="O704">
+        <v>3</v>
+      </c>
+      <c r="P704" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="705" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A705" t="s">
+        <v>740</v>
+      </c>
+      <c r="B705">
+        <v>2</v>
+      </c>
+      <c r="C705" t="s">
+        <v>17</v>
+      </c>
+      <c r="D705" t="s">
+        <v>27</v>
+      </c>
+      <c r="E705" t="s">
+        <v>25</v>
+      </c>
+      <c r="F705" t="s">
+        <v>17</v>
+      </c>
+      <c r="J705" t="s">
+        <v>17</v>
+      </c>
+      <c r="N705" t="s">
+        <v>20</v>
+      </c>
+      <c r="P705" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="706" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A706" t="s">
+        <v>741</v>
+      </c>
+      <c r="B706">
+        <v>5</v>
+      </c>
+      <c r="C706" t="s">
+        <v>17</v>
+      </c>
+      <c r="D706" t="s">
+        <v>34</v>
+      </c>
+      <c r="F706" t="s">
+        <v>20</v>
+      </c>
+      <c r="H706" t="s">
+        <v>42</v>
+      </c>
+      <c r="I706">
+        <v>21</v>
+      </c>
+      <c r="J706" t="s">
+        <v>20</v>
+      </c>
+      <c r="L706" t="s">
+        <v>42</v>
+      </c>
+      <c r="M706">
+        <v>21</v>
+      </c>
+      <c r="N706" t="s">
+        <v>17</v>
+      </c>
+      <c r="O706">
+        <v>3</v>
+      </c>
+      <c r="P706" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="707" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A707" t="s">
+        <v>742</v>
+      </c>
+      <c r="B707">
+        <v>2</v>
+      </c>
+      <c r="C707" t="s">
+        <v>17</v>
+      </c>
+      <c r="D707" t="s">
+        <v>18</v>
+      </c>
+      <c r="E707" t="s">
+        <v>25</v>
+      </c>
+      <c r="F707" t="s">
+        <v>17</v>
+      </c>
+      <c r="J707" t="s">
+        <v>17</v>
+      </c>
+      <c r="N707" t="s">
+        <v>20</v>
+      </c>
+      <c r="P707" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="708" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A708" t="s">
+        <v>743</v>
+      </c>
+      <c r="B708">
+        <v>6</v>
+      </c>
+      <c r="C708" t="s">
+        <v>17</v>
+      </c>
+      <c r="D708" t="s">
+        <v>34</v>
+      </c>
+      <c r="F708" t="s">
+        <v>17</v>
+      </c>
+      <c r="J708" t="s">
+        <v>17</v>
+      </c>
+      <c r="N708" t="s">
+        <v>20</v>
+      </c>
+      <c r="P708" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="709" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A709" t="s">
+        <v>744</v>
+      </c>
+      <c r="B709">
+        <v>0</v>
+      </c>
+      <c r="C709" t="s">
+        <v>20</v>
+      </c>
+      <c r="D709" t="s">
+        <v>18</v>
+      </c>
+      <c r="E709" t="s">
+        <v>28</v>
+      </c>
+      <c r="F709" t="s">
+        <v>20</v>
+      </c>
+      <c r="I709">
+        <v>5</v>
+      </c>
+      <c r="J709" t="s">
+        <v>17</v>
+      </c>
+      <c r="N709" t="s">
+        <v>20</v>
+      </c>
+      <c r="O709">
+        <v>3</v>
+      </c>
+      <c r="P709" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="710" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A710" t="s">
+        <v>745</v>
+      </c>
+      <c r="B710">
+        <v>2</v>
+      </c>
+      <c r="C710" t="s">
+        <v>20</v>
+      </c>
+      <c r="D710" t="s">
+        <v>34</v>
+      </c>
+      <c r="E710" t="s">
+        <v>28</v>
+      </c>
+      <c r="F710" t="s">
+        <v>20</v>
+      </c>
+      <c r="H710" t="s">
+        <v>34</v>
+      </c>
+      <c r="I710">
+        <v>10</v>
+      </c>
+      <c r="J710" t="s">
+        <v>17</v>
+      </c>
+      <c r="N710" t="s">
+        <v>20</v>
+      </c>
+      <c r="P710" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="711" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A711" t="s">
+        <v>746</v>
+      </c>
+      <c r="B711">
+        <v>4</v>
+      </c>
+      <c r="C711" t="s">
+        <v>17</v>
+      </c>
+      <c r="D711" t="s">
+        <v>44</v>
+      </c>
+      <c r="E711" t="s">
+        <v>28</v>
+      </c>
+      <c r="F711" t="s">
+        <v>17</v>
+      </c>
+      <c r="J711" t="s">
+        <v>20</v>
+      </c>
+      <c r="M711">
+        <v>34</v>
+      </c>
+      <c r="N711" t="s">
+        <v>17</v>
+      </c>
+      <c r="O711" t="s">
+        <v>48</v>
+      </c>
+      <c r="P711" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="712" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A712" t="s">
+        <v>747</v>
+      </c>
+      <c r="B712">
+        <v>6</v>
+      </c>
+      <c r="C712" t="s">
+        <v>17</v>
+      </c>
+      <c r="D712" t="s">
+        <v>55</v>
+      </c>
+      <c r="E712" t="s">
+        <v>28</v>
+      </c>
+      <c r="F712" t="s">
+        <v>20</v>
+      </c>
+      <c r="I712">
+        <v>19</v>
+      </c>
+      <c r="J712" t="s">
+        <v>17</v>
+      </c>
+      <c r="N712" t="s">
+        <v>17</v>
+      </c>
+      <c r="O712">
+        <v>3</v>
+      </c>
+      <c r="P712" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="713" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A713" t="s">
+        <v>748</v>
+      </c>
+      <c r="B713">
+        <v>2</v>
+      </c>
+      <c r="C713" t="s">
+        <v>17</v>
+      </c>
+      <c r="D713" t="s">
+        <v>34</v>
+      </c>
+      <c r="E713" t="s">
+        <v>28</v>
+      </c>
+      <c r="F713" t="s">
+        <v>20</v>
+      </c>
+      <c r="I713">
+        <v>11</v>
+      </c>
+      <c r="J713" t="s">
+        <v>17</v>
+      </c>
+      <c r="N713" t="s">
+        <v>20</v>
+      </c>
+      <c r="P713" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="714" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A714" t="s">
+        <v>749</v>
+      </c>
+      <c r="B714">
+        <v>2</v>
+      </c>
+      <c r="C714" t="s">
+        <v>17</v>
+      </c>
+      <c r="D714" t="s">
+        <v>44</v>
+      </c>
+      <c r="E714" t="s">
+        <v>28</v>
+      </c>
+      <c r="F714" t="s">
+        <v>20</v>
+      </c>
+      <c r="I714">
+        <v>15</v>
+      </c>
+      <c r="J714" t="s">
+        <v>17</v>
+      </c>
+      <c r="N714" t="s">
+        <v>17</v>
+      </c>
+      <c r="P714" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="715" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A715" t="s">
+        <v>750</v>
+      </c>
+      <c r="B715">
+        <v>1</v>
+      </c>
+      <c r="C715" t="s">
+        <v>17</v>
+      </c>
+      <c r="D715" t="s">
+        <v>44</v>
+      </c>
+      <c r="E715" t="s">
+        <v>28</v>
+      </c>
+      <c r="F715" t="s">
+        <v>17</v>
+      </c>
+      <c r="J715" t="s">
+        <v>17</v>
+      </c>
+      <c r="N715" t="s">
+        <v>17</v>
+      </c>
+      <c r="P715" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="716" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A716" t="s">
+        <v>751</v>
+      </c>
+      <c r="B716">
+        <v>2</v>
+      </c>
+      <c r="C716" t="s">
+        <v>20</v>
+      </c>
+      <c r="D716" t="s">
+        <v>18</v>
+      </c>
+      <c r="E716" t="s">
+        <v>25</v>
+      </c>
+      <c r="F716" t="s">
+        <v>17</v>
+      </c>
+      <c r="J716" t="s">
+        <v>17</v>
+      </c>
+      <c r="N716" t="s">
+        <v>20</v>
+      </c>
+      <c r="P716" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="717" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A717" t="s">
+        <v>752</v>
+      </c>
+      <c r="B717">
+        <v>6</v>
+      </c>
+      <c r="C717" t="s">
+        <v>17</v>
+      </c>
+      <c r="D717" t="s">
+        <v>44</v>
+      </c>
+      <c r="E717" t="s">
+        <v>25</v>
+      </c>
+      <c r="F717" t="s">
+        <v>17</v>
+      </c>
+      <c r="J717" t="s">
+        <v>17</v>
+      </c>
+      <c r="N717" t="s">
+        <v>17</v>
+      </c>
+      <c r="P717" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="718" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A718" t="s">
+        <v>753</v>
+      </c>
+      <c r="B718">
+        <v>2</v>
+      </c>
+      <c r="C718" t="s">
+        <v>20</v>
+      </c>
+      <c r="D718" t="s">
+        <v>44</v>
+      </c>
+      <c r="E718" t="s">
+        <v>25</v>
+      </c>
+      <c r="F718" t="s">
+        <v>17</v>
+      </c>
+      <c r="J718" t="s">
+        <v>17</v>
+      </c>
+      <c r="N718" t="s">
+        <v>17</v>
+      </c>
+      <c r="P718" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="719" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A719" t="s">
+        <v>754</v>
+      </c>
+      <c r="B719">
+        <v>5</v>
+      </c>
+      <c r="C719" t="s">
+        <v>20</v>
+      </c>
+      <c r="D719" t="s">
+        <v>44</v>
+      </c>
+      <c r="E719" t="s">
+        <v>25</v>
+      </c>
+      <c r="F719" t="s">
+        <v>20</v>
+      </c>
+      <c r="H719" t="s">
+        <v>42</v>
+      </c>
+      <c r="I719">
+        <v>10</v>
+      </c>
+      <c r="J719" t="s">
+        <v>17</v>
+      </c>
+      <c r="N719" t="s">
+        <v>17</v>
+      </c>
+      <c r="O719">
+        <v>3</v>
+      </c>
+      <c r="P719" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="720" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A720" t="s">
+        <v>755</v>
+      </c>
+      <c r="B720">
+        <v>2</v>
+      </c>
+      <c r="C720" t="s">
+        <v>17</v>
+      </c>
+      <c r="D720" t="s">
+        <v>34</v>
+      </c>
+      <c r="E720" t="s">
+        <v>25</v>
+      </c>
+      <c r="F720" t="s">
+        <v>17</v>
+      </c>
+      <c r="J720" t="s">
+        <v>17</v>
+      </c>
+      <c r="N720" t="s">
+        <v>20</v>
+      </c>
+      <c r="P720" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="721" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A721" t="s">
+        <v>756</v>
+      </c>
+      <c r="B721">
+        <v>6</v>
+      </c>
+      <c r="C721" t="s">
+        <v>17</v>
+      </c>
+      <c r="D721" t="s">
+        <v>44</v>
+      </c>
+      <c r="E721" t="s">
+        <v>25</v>
+      </c>
+      <c r="F721" t="s">
+        <v>17</v>
+      </c>
+      <c r="J721" t="s">
+        <v>17</v>
+      </c>
+      <c r="N721" t="s">
+        <v>17</v>
+      </c>
+      <c r="P721" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="722" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A722" t="s">
+        <v>757</v>
+      </c>
+      <c r="B722">
+        <v>2</v>
+      </c>
+      <c r="C722" t="s">
+        <v>17</v>
+      </c>
+      <c r="D722" t="s">
+        <v>55</v>
+      </c>
+      <c r="E722" t="s">
+        <v>25</v>
+      </c>
+      <c r="F722" t="s">
+        <v>20</v>
+      </c>
+      <c r="I722">
+        <v>7</v>
+      </c>
+      <c r="J722" t="s">
+        <v>17</v>
+      </c>
+      <c r="N722" t="s">
+        <v>20</v>
+      </c>
+      <c r="P722" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="723" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A723" t="s">
+        <v>758</v>
+      </c>
+      <c r="B723">
+        <v>5</v>
+      </c>
+      <c r="C723" t="s">
+        <v>17</v>
+      </c>
+      <c r="F723" t="s">
+        <v>20</v>
+      </c>
+      <c r="H723" t="s">
+        <v>42</v>
+      </c>
+      <c r="I723">
+        <v>23</v>
+      </c>
+      <c r="J723" t="s">
+        <v>17</v>
+      </c>
+      <c r="N723" t="s">
+        <v>17</v>
+      </c>
+      <c r="O723">
+        <v>3</v>
+      </c>
+      <c r="P723" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="724" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A724" t="s">
+        <v>759</v>
+      </c>
+      <c r="B724">
+        <v>2</v>
+      </c>
+      <c r="C724" t="s">
+        <v>17</v>
+      </c>
+      <c r="D724" t="s">
+        <v>44</v>
+      </c>
+      <c r="E724" t="s">
+        <v>25</v>
+      </c>
+      <c r="F724" t="s">
+        <v>17</v>
+      </c>
+      <c r="J724" t="s">
+        <v>17</v>
+      </c>
+      <c r="N724" t="s">
+        <v>20</v>
+      </c>
+      <c r="P724" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="725" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A725" t="s">
+        <v>760</v>
+      </c>
+      <c r="B725">
+        <v>4</v>
+      </c>
+      <c r="C725" t="s">
+        <v>20</v>
+      </c>
+      <c r="D725" t="s">
+        <v>27</v>
+      </c>
+      <c r="E725" t="s">
+        <v>25</v>
+      </c>
+      <c r="F725" t="s">
+        <v>20</v>
+      </c>
+      <c r="H725" t="s">
+        <v>42</v>
+      </c>
+      <c r="I725">
+        <v>5</v>
+      </c>
+      <c r="J725" t="s">
+        <v>20</v>
+      </c>
+      <c r="M725">
+        <v>14</v>
+      </c>
+      <c r="N725" t="s">
+        <v>17</v>
+      </c>
+      <c r="O725">
+        <v>1</v>
+      </c>
+      <c r="P725" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="726" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A726" t="s">
+        <v>761</v>
+      </c>
+      <c r="B726">
+        <v>2</v>
+      </c>
+      <c r="C726" t="s">
+        <v>17</v>
+      </c>
+      <c r="D726" t="s">
+        <v>44</v>
+      </c>
+      <c r="E726" t="s">
+        <v>28</v>
+      </c>
+      <c r="F726" t="s">
+        <v>20</v>
+      </c>
+      <c r="J726" t="s">
+        <v>17</v>
+      </c>
+      <c r="N726" t="s">
+        <v>20</v>
+      </c>
+      <c r="O726">
+        <v>1</v>
+      </c>
+      <c r="P726" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="727" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A727" t="s">
+        <v>762</v>
+      </c>
+      <c r="B727">
+        <v>2</v>
+      </c>
+      <c r="C727" t="s">
+        <v>20</v>
+      </c>
+      <c r="D727" t="s">
+        <v>34</v>
+      </c>
+      <c r="E727" t="s">
+        <v>25</v>
+      </c>
+      <c r="F727" t="s">
+        <v>17</v>
+      </c>
+      <c r="J727" t="s">
+        <v>17</v>
+      </c>
+      <c r="N727" t="s">
+        <v>20</v>
+      </c>
+      <c r="P727" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="728" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A728" t="s">
+        <v>763</v>
+      </c>
+      <c r="B728">
+        <v>2</v>
+      </c>
+      <c r="C728" t="s">
+        <v>20</v>
+      </c>
+      <c r="D728" t="s">
+        <v>55</v>
+      </c>
+      <c r="E728" t="s">
+        <v>25</v>
+      </c>
+      <c r="F728" t="s">
+        <v>17</v>
+      </c>
+      <c r="J728" t="s">
+        <v>17</v>
+      </c>
+      <c r="N728" t="s">
+        <v>20</v>
+      </c>
+      <c r="P728" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="729" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A729" t="s">
+        <v>764</v>
+      </c>
+      <c r="B729">
+        <v>1</v>
+      </c>
+      <c r="C729" t="s">
+        <v>20</v>
+      </c>
+      <c r="D729" t="s">
+        <v>32</v>
+      </c>
+      <c r="E729" t="s">
+        <v>28</v>
+      </c>
+      <c r="F729" t="s">
+        <v>17</v>
+      </c>
+      <c r="J729" t="s">
+        <v>17</v>
+      </c>
+      <c r="N729" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/GT_gpt5_2_1.xlsx
+++ b/GT_gpt5_2_1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkats\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkats\Desktop\MEDICAL REPORTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{91D4C75B-B2CD-4F57-8278-FDCAB022D852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03BFA620-3998-457E-AAD4-BB9B56F8E461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{A3F4C6B1-7A32-46D0-81EC-1870D7AD2687}"/>
+    <workbookView xWindow="10886" yWindow="0" windowWidth="11143" windowHeight="13080" xr2:uid="{A3F4C6B1-7A32-46D0-81EC-1870D7AD2687}"/>
   </bookViews>
   <sheets>
     <sheet name="GT_gpt5_2_1" sheetId="1" r:id="rId1"/>
@@ -5595,6 +5595,9 @@
       <c r="A75" t="s">
         <v>110</v>
       </c>
+      <c r="B75">
+        <v>3</v>
+      </c>
       <c r="C75" t="s">
         <v>17</v>
       </c>
@@ -8535,6 +8538,9 @@
     <row r="164" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A164" t="s">
         <v>199</v>
+      </c>
+      <c r="B164">
+        <v>2</v>
       </c>
       <c r="C164" t="s">
         <v>17</v>
